--- a/data/teams/leagues/Averages_Japan_J1_League_2025.xlsx
+++ b/data/teams/leagues/Averages_Japan_J1_League_2025.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable" displayName="AveragesTable" ref="A1:EC21" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Japan_J1_L" displayName="AveragesTable_Japan_J1_L" ref="A1:EC21" headerRowCount="1">
   <autoFilter ref="A1:EC21"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>

--- a/data/teams/leagues/Averages_Japan_J1_League_2025.xlsx
+++ b/data/teams/leagues/Averages_Japan_J1_League_2025.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
         <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="G2" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="H2" t="n">
-        <v>97.44</v>
+        <v>97.79000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>-0.11</v>
       </c>
       <c r="J2" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="K2" t="n">
-        <v>4.89</v>
+        <v>4.79</v>
       </c>
       <c r="L2" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="M2" t="n">
-        <v>42.83</v>
+        <v>42.79</v>
       </c>
       <c r="N2" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="O2" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="P2" t="n">
-        <v>9.779999999999999</v>
+        <v>9.74</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.33</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>7.72</v>
+        <v>7.74</v>
       </c>
       <c r="S2" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="T2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="U2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="V2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>55.94</v>
+        <v>55.32</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>13</v>
+        <v>12.58</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.390000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.61</v>
+        <v>3.47</v>
       </c>
       <c r="AC2" t="n">
-        <v>19.28</v>
+        <v>19.37</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF2" t="n">
         <v>0.11</v>
@@ -1550,70 +1550,70 @@
         <v>0.83</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.17</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="BL2" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.72</v>
+        <v>4.65</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.44</v>
+        <v>4.41</v>
       </c>
       <c r="BR2" t="n">
-        <v>94.44</v>
+        <v>94.59</v>
       </c>
       <c r="BS2" t="n">
-        <v>69.44</v>
+        <v>70.27</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>51.35</v>
       </c>
       <c r="BU2" t="n">
-        <v>30.56</v>
+        <v>32.43</v>
       </c>
       <c r="BV2" t="n">
-        <v>13.89</v>
+        <v>13.51</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.33</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="BX2" t="n">
-        <v>58.33</v>
+        <v>59.46</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.95</v>
+        <v>3.04</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.42</v>
+        <v>3.47</v>
       </c>
       <c r="CC2" t="n">
         <v>3.62</v>
@@ -1622,13 +1622,13 @@
         <v>3.89</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="CH2" t="n">
         <v>1.34</v>
@@ -1655,10 +1655,10 @@
         <v>1.38</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="CR2" t="n">
         <v>1.5</v>
@@ -1679,7 +1679,7 @@
         <v>1.97</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY2" t="n">
         <v>2.01</v>
@@ -1694,10 +1694,10 @@
         <v>1.39</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.17</v>
+        <v>4.13</v>
       </c>
       <c r="DE2" t="n">
         <v>0.08</v>
@@ -1706,40 +1706,40 @@
         <v>0.7</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="DH2" t="n">
-        <v>91.42</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="DI2" t="n">
         <v>-0.14</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.61</v>
+        <v>4.57</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="DM2" t="n">
-        <v>40.16</v>
+        <v>40.22</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="DP2" t="n">
-        <v>9.640000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DQ2" t="n">
-        <v>8.720000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.359999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="DS2" t="n">
         <v>0.08</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>54.75</v>
+        <v>54.46</v>
       </c>
       <c r="DW2" t="n">
         <v>0.03</v>
       </c>
       <c r="DX2" t="n">
-        <v>11.78</v>
+        <v>11.6</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.48</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="EA2" t="n">
-        <v>20.03</v>
+        <v>20.06</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
         <v>18</v>
@@ -1794,82 +1794,82 @@
         <v>0.11</v>
       </c>
       <c r="F3" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="G3" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="H3" t="n">
-        <v>91.22</v>
+        <v>90.58</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="K3" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="L3" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="M3" t="n">
-        <v>45.17</v>
+        <v>45.42</v>
       </c>
       <c r="N3" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="P3" t="n">
-        <v>12.39</v>
+        <v>12.63</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.11</v>
+        <v>11.95</v>
       </c>
       <c r="R3" t="n">
-        <v>7.22</v>
+        <v>7.11</v>
       </c>
       <c r="S3" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="U3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="V3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>45.11</v>
+        <v>44.37</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="Z3" t="n">
-        <v>13.22</v>
+        <v>13.47</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.67</v>
+        <v>8.84</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.56</v>
+        <v>4.63</v>
       </c>
       <c r="AC3" t="n">
-        <v>20.61</v>
+        <v>21.11</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AF3" t="n">
         <v>0.06</v>
@@ -1953,70 +1953,70 @@
         <v>1.28</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="BH3" t="n">
         <v>8.029999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="BN3" t="n">
         <v>1.11</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.69</v>
+        <v>3.65</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="BR3" t="n">
-        <v>80.56</v>
+        <v>81.08</v>
       </c>
       <c r="BS3" t="n">
-        <v>47.22</v>
+        <v>45.95</v>
       </c>
       <c r="BT3" t="n">
-        <v>33.33</v>
+        <v>32.43</v>
       </c>
       <c r="BU3" t="n">
-        <v>16.67</v>
+        <v>16.22</v>
       </c>
       <c r="BV3" t="n">
-        <v>8.33</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.56</v>
+        <v>5.41</v>
       </c>
       <c r="BX3" t="n">
-        <v>41.67</v>
+        <v>40.54</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CA3" t="n">
         <v>3.08</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CC3" t="n">
         <v>3.5</v>
@@ -2025,10 +2025,10 @@
         <v>3.68</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CG3" t="n">
         <v>2.38</v>
@@ -2037,49 +2037,49 @@
         <v>1.27</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CK3" t="n">
         <v>1.67</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CN3" t="n">
         <v>1.68</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CQ3" t="n">
-        <v>4.97</v>
+        <v>4.94</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CU3" t="n">
         <v>1.35</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CX3" t="n">
         <v>1.73</v>
@@ -2088,94 +2088,94 @@
         <v>2.18</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DA3" t="n">
         <v>1.67</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="DD3" t="n">
-        <v>5.41</v>
+        <v>5.37</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="DG3" t="n">
         <v>2.08</v>
       </c>
       <c r="DH3" t="n">
-        <v>94.28</v>
+        <v>93.86</v>
       </c>
       <c r="DI3" t="n">
         <v>-0.03</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="DK3" t="n">
         <v>4.11</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="DM3" t="n">
-        <v>45.78</v>
+        <v>45.89</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="DO3" t="n">
         <v>2</v>
       </c>
       <c r="DP3" t="n">
-        <v>12.53</v>
+        <v>12.65</v>
       </c>
       <c r="DQ3" t="n">
-        <v>10.94</v>
+        <v>10.89</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.72</v>
+        <v>7.65</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>46.8</v>
+        <v>46.38</v>
       </c>
       <c r="DW3" t="n">
         <v>0.08</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.83</v>
+        <v>12.97</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.92</v>
+        <v>9</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.92</v>
+        <v>3.97</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.06</v>
+        <v>20.33</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C4" t="n">
         <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
         <v>0.28</v>
@@ -2275,139 +2275,139 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AG4" t="n">
         <v>0.89</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
-        <v>100.44</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.22</v>
+        <v>-0.21</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.17</v>
+        <v>4.26</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="AN4" t="n">
-        <v>50.28</v>
+        <v>50.16</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.5</v>
+        <v>8.68</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.67</v>
+        <v>11</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.94</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>56.33</v>
+        <v>56.63</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="BA4" t="n">
-        <v>12.67</v>
+        <v>12.74</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.78</v>
+        <v>7.89</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.89</v>
+        <v>4.84</v>
       </c>
       <c r="BD4" t="n">
-        <v>21.56</v>
+        <v>21.63</v>
       </c>
       <c r="BE4" t="n">
         <v>1.51</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="BH4" t="n">
-        <v>11.06</v>
+        <v>11.03</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="BJ4" t="n">
         <v>0.92</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.81</v>
+        <v>4.65</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.19</v>
+        <v>6</v>
       </c>
       <c r="BR4" t="n">
-        <v>97.22</v>
+        <v>97.3</v>
       </c>
       <c r="BS4" t="n">
-        <v>86.11</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>58.33</v>
+        <v>59.46</v>
       </c>
       <c r="BU4" t="n">
-        <v>30.56</v>
+        <v>32.43</v>
       </c>
       <c r="BV4" t="n">
-        <v>16.67</v>
+        <v>16.22</v>
       </c>
       <c r="BW4" t="n">
-        <v>11.11</v>
+        <v>10.81</v>
       </c>
       <c r="BX4" t="n">
-        <v>72.22</v>
+        <v>72.97</v>
       </c>
       <c r="BY4" t="n">
         <v>2.34</v>
@@ -2419,28 +2419,28 @@
         <v>3.41</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="CE4" t="n">
         <v>1.37</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.69</v>
@@ -2449,10 +2449,10 @@
         <v>1.43</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CN4" t="n">
         <v>2.01</v>
@@ -2461,16 +2461,16 @@
         <v>1.27</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="CR4" t="n">
         <v>1.41</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CT4" t="n">
         <v>3.03</v>
@@ -2479,7 +2479,7 @@
         <v>1.46</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CW4" t="n">
         <v>1.72</v>
@@ -2500,82 +2500,82 @@
         <v>1.28</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF4" t="n">
         <v>0.84</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="DH4" t="n">
-        <v>96.69</v>
+        <v>95.92</v>
       </c>
       <c r="DI4" t="n">
         <v>-0.11</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.64</v>
+        <v>5.65</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
       <c r="DM4" t="n">
-        <v>50.78</v>
+        <v>50.7</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="DP4" t="n">
-        <v>8.91</v>
+        <v>9</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.64</v>
+        <v>11.78</v>
       </c>
       <c r="DR4" t="n">
         <v>9.08</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>54.92</v>
+        <v>55.11</v>
       </c>
       <c r="DW4" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="DX4" t="n">
         <v>13.89</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.859999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.03</v>
+        <v>5</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.64</v>
+        <v>20.7</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="EC4" t="n">
         <v>1.08</v>
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
         <v>18</v>
@@ -2600,82 +2600,82 @@
         <v>0.11</v>
       </c>
       <c r="F5" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="G5" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="H5" t="n">
-        <v>93.44</v>
+        <v>93.16</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="J5" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="K5" t="n">
-        <v>5.5</v>
+        <v>5.26</v>
       </c>
       <c r="L5" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="M5" t="n">
-        <v>50.22</v>
+        <v>50</v>
       </c>
       <c r="N5" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="O5" t="n">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="P5" t="n">
-        <v>11.17</v>
+        <v>11.21</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.5</v>
+        <v>8.42</v>
       </c>
       <c r="R5" t="n">
-        <v>9.06</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="V5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>42.78</v>
+        <v>42.58</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="Z5" t="n">
-        <v>12</v>
+        <v>11.95</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.94</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>25.22</v>
+        <v>25.21</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF5" t="n">
         <v>0.06</v>
@@ -2759,64 +2759,64 @@
         <v>1.11</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.44</v>
+        <v>10.3</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.92</v>
+        <v>4.84</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.47</v>
+        <v>5.41</v>
       </c>
       <c r="BR5" t="n">
-        <v>91.67</v>
+        <v>91.89</v>
       </c>
       <c r="BS5" t="n">
-        <v>58.33</v>
+        <v>56.76</v>
       </c>
       <c r="BT5" t="n">
-        <v>33.33</v>
+        <v>32.43</v>
       </c>
       <c r="BU5" t="n">
-        <v>11.11</v>
+        <v>10.81</v>
       </c>
       <c r="BV5" t="n">
-        <v>5.56</v>
+        <v>5.41</v>
       </c>
       <c r="BW5" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BX5" t="n">
-        <v>41.67</v>
+        <v>40.54</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="CA5" t="n">
         <v>3.18</v>
@@ -2831,10 +2831,10 @@
         <v>4.05</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CG5" t="n">
         <v>2.55</v>
@@ -2843,7 +2843,7 @@
         <v>1.32</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.98</v>
@@ -2852,7 +2852,7 @@
         <v>1.49</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CM5" t="n">
         <v>2.48</v>
@@ -2861,16 +2861,16 @@
         <v>1.91</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CP5" t="n">
         <v>2.29</v>
       </c>
       <c r="CQ5" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CS5" t="n">
         <v>3.24</v>
@@ -2882,13 +2882,13 @@
         <v>1.37</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CW5" t="n">
         <v>2.05</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY5" t="n">
         <v>1.9</v>
@@ -2903,52 +2903,52 @@
         <v>1.44</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DD5" t="n">
-        <v>4.57</v>
+        <v>4.55</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="DH5" t="n">
-        <v>93.86</v>
+        <v>93.7</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="DK5" t="n">
-        <v>5</v>
+        <v>4.89</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DM5" t="n">
         <v>45.97</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.06</v>
+        <v>11.08</v>
       </c>
       <c r="DQ5" t="n">
-        <v>8.91</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.029999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="DS5" t="n">
         <v>0.03</v>
@@ -2960,16 +2960,16 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>42.17</v>
+        <v>42.08</v>
       </c>
       <c r="DW5" t="n">
         <v>0.03</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.56</v>
+        <v>10.57</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.58</v>
+        <v>7.59</v>
       </c>
       <c r="DZ5" t="n">
         <v>2.97</v>
@@ -2978,10 +2978,10 @@
         <v>25.11</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C6" t="n">
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
         <v>0.11</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AI6" t="n">
-        <v>97.28</v>
+        <v>96.37</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.06</v>
+        <v>5</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="AN6" t="n">
-        <v>51.78</v>
+        <v>51</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10.83</v>
+        <v>10.74</v>
       </c>
       <c r="AR6" t="n">
-        <v>8.890000000000001</v>
+        <v>9.32</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.94</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>51.94</v>
+        <v>52.84</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="BA6" t="n">
-        <v>12.61</v>
+        <v>12.37</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.109999999999999</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.5</v>
+        <v>4.32</v>
       </c>
       <c r="BD6" t="n">
-        <v>20.56</v>
+        <v>20.42</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.06</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="BL6" t="n">
         <v>0.89</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.92</v>
+        <v>3.86</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.06</v>
+        <v>5.08</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.44</v>
+        <v>94.59</v>
       </c>
       <c r="BS6" t="n">
-        <v>66.67</v>
+        <v>64.86</v>
       </c>
       <c r="BT6" t="n">
-        <v>47.22</v>
+        <v>45.95</v>
       </c>
       <c r="BU6" t="n">
-        <v>33.33</v>
+        <v>32.43</v>
       </c>
       <c r="BV6" t="n">
-        <v>19.44</v>
+        <v>18.92</v>
       </c>
       <c r="BW6" t="n">
-        <v>11.11</v>
+        <v>10.81</v>
       </c>
       <c r="BX6" t="n">
-        <v>41.67</v>
+        <v>40.54</v>
       </c>
       <c r="BY6" t="n">
         <v>2.3</v>
@@ -3222,25 +3222,25 @@
         <v>2.44</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CB6" t="n">
         <v>3.48</v>
       </c>
       <c r="CC6" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CE6" t="n">
         <v>1.42</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CH6" t="n">
         <v>1.36</v>
@@ -3255,28 +3255,28 @@
         <v>1.52</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CO6" t="n">
         <v>1.34</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.69</v>
+        <v>3.71</v>
       </c>
       <c r="CR6" t="n">
         <v>1.47</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CT6" t="n">
         <v>2.81</v>
@@ -3291,16 +3291,16 @@
         <v>1.9</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DB6" t="n">
         <v>1.36</v>
@@ -3312,79 +3312,79 @@
         <v>3.91</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="DH6" t="n">
-        <v>101.22</v>
+        <v>100.65</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.89</v>
+        <v>4.86</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM6" t="n">
-        <v>54.7</v>
+        <v>54.22</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.58</v>
+        <v>10.54</v>
       </c>
       <c r="DQ6" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.33</v>
+        <v>7.4</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>51.92</v>
+        <v>52.38</v>
       </c>
       <c r="DW6" t="n">
         <v>0.08</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.34</v>
+        <v>13.19</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.94</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.39</v>
+        <v>4.3</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.98</v>
+        <v>20.89</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7" t="n">
         <v>18</v>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
         <v>0.17</v>
@@ -3484,139 +3484,139 @@
         <v>1.33</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="AI7" t="n">
-        <v>95.44</v>
+        <v>94.16</v>
       </c>
       <c r="AJ7" t="n">
         <v>-0.11</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.83</v>
+        <v>4.79</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
       <c r="AN7" t="n">
-        <v>42.11</v>
+        <v>41.84</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="AP7" t="n">
         <v>2.11</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11.28</v>
+        <v>11.37</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.28</v>
+        <v>12.32</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.279999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>51</v>
+        <v>50.68</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>11.28</v>
+        <v>11.32</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.56</v>
+        <v>7.53</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.72</v>
+        <v>3.79</v>
       </c>
       <c r="BD7" t="n">
-        <v>22.94</v>
+        <v>22.58</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.94</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.56</v>
+        <v>5.54</v>
       </c>
       <c r="BR7" t="n">
-        <v>94.44</v>
+        <v>94.59</v>
       </c>
       <c r="BS7" t="n">
-        <v>63.89</v>
+        <v>62.16</v>
       </c>
       <c r="BT7" t="n">
-        <v>47.22</v>
+        <v>45.95</v>
       </c>
       <c r="BU7" t="n">
-        <v>19.44</v>
+        <v>18.92</v>
       </c>
       <c r="BV7" t="n">
-        <v>5.56</v>
+        <v>5.41</v>
       </c>
       <c r="BW7" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>48.65</v>
       </c>
       <c r="BY7" t="n">
         <v>2.35</v>
@@ -3628,28 +3628,28 @@
         <v>3.23</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="CE7" t="n">
         <v>1.43</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.84</v>
@@ -3658,7 +3658,7 @@
         <v>1.51</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CM7" t="n">
         <v>2.42</v>
@@ -3667,13 +3667,13 @@
         <v>1.89</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.79</v>
+        <v>3.81</v>
       </c>
       <c r="CR7" t="n">
         <v>1.47</v>
@@ -3682,16 +3682,16 @@
         <v>3.05</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CU7" t="n">
         <v>1.41</v>
       </c>
       <c r="CV7" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CX7" t="n">
         <v>1.54</v>
@@ -3703,58 +3703,58 @@
         <v>2.39</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DB7" t="n">
         <v>1.37</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="DH7" t="n">
-        <v>99.66</v>
+        <v>98.89</v>
       </c>
       <c r="DI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.11</v>
+        <v>5.08</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="DM7" t="n">
-        <v>45.5</v>
+        <v>45.27</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="DO7" t="n">
         <v>2.16</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.73</v>
+        <v>10.79</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.3</v>
+        <v>12.32</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.300000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="DS7" t="n">
         <v>0.14</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>51.75</v>
+        <v>51.57</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.06</v>
+        <v>12.05</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.83</v>
+        <v>7.81</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.22</v>
+        <v>4.24</v>
       </c>
       <c r="EA7" t="n">
-        <v>23.83</v>
+        <v>23.62</v>
       </c>
       <c r="EB7" t="n">
         <v>1.39</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" t="n">
         <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3890,136 +3890,136 @@
         <v>0.11</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AI8" t="n">
-        <v>106.39</v>
+        <v>105.79</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AL8" t="n">
-        <v>5</v>
+        <v>4.84</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AN8" t="n">
-        <v>49.28</v>
+        <v>48.68</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10.83</v>
+        <v>10.63</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.220000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="AS8" t="n">
-        <v>8</v>
+        <v>7.84</v>
       </c>
       <c r="AT8" t="n">
         <v>1</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>57.89</v>
+        <v>57.79</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>12.5</v>
+        <v>12.58</v>
       </c>
       <c r="BB8" t="n">
-        <v>8</v>
+        <v>7.89</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.5</v>
+        <v>4.68</v>
       </c>
       <c r="BD8" t="n">
-        <v>22.78</v>
+        <v>22.58</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.33</v>
+        <v>10.19</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.36</v>
+        <v>4.3</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.97</v>
+        <v>5.89</v>
       </c>
       <c r="BR8" t="n">
-        <v>91.67</v>
+        <v>91.89</v>
       </c>
       <c r="BS8" t="n">
-        <v>72.22</v>
+        <v>72.97</v>
       </c>
       <c r="BT8" t="n">
-        <v>36.11</v>
+        <v>37.84</v>
       </c>
       <c r="BU8" t="n">
-        <v>19.44</v>
+        <v>21.62</v>
       </c>
       <c r="BV8" t="n">
-        <v>13.89</v>
+        <v>13.51</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.33</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="BX8" t="n">
-        <v>47.22</v>
+        <v>48.65</v>
       </c>
       <c r="BY8" t="n">
         <v>2.13</v>
@@ -4028,25 +4028,25 @@
         <v>2.22</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="CC8" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="CD8" t="n">
         <v>2.64</v>
       </c>
-      <c r="CD8" t="n">
-        <v>2.71</v>
-      </c>
       <c r="CE8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="CH8" t="n">
         <v>1.35</v>
@@ -4070,13 +4070,13 @@
         <v>1.93</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="CR8" t="n">
         <v>1.5</v>
@@ -4112,85 +4112,85 @@
         <v>1.39</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.17</v>
+        <v>4.13</v>
       </c>
       <c r="DE8" t="n">
         <v>0.06</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="DH8" t="n">
-        <v>108.8</v>
+        <v>108.43</v>
       </c>
       <c r="DI8" t="n">
         <v>0.03</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.47</v>
+        <v>5.38</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="DM8" t="n">
-        <v>52.78</v>
+        <v>52.38</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="DP8" t="n">
-        <v>10.33</v>
+        <v>10.24</v>
       </c>
       <c r="DQ8" t="n">
-        <v>8.56</v>
+        <v>8.57</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.89</v>
+        <v>7.81</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>60.22</v>
+        <v>60.11</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.64</v>
+        <v>12.68</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.34</v>
+        <v>8.27</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.31</v>
+        <v>4.4</v>
       </c>
       <c r="EA8" t="n">
-        <v>22.7</v>
+        <v>22.59</v>
       </c>
       <c r="EB8" t="n">
         <v>1.49</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="9">
@@ -4200,61 +4200,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
         <v>18</v>
       </c>
       <c r="E9" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="F9" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="G9" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H9" t="n">
-        <v>92.67</v>
+        <v>92</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="K9" t="n">
-        <v>4.83</v>
+        <v>4.74</v>
       </c>
       <c r="L9" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="M9" t="n">
-        <v>46.11</v>
+        <v>45.47</v>
       </c>
       <c r="N9" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="O9" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="P9" t="n">
-        <v>9.33</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.67</v>
+        <v>11.47</v>
       </c>
       <c r="R9" t="n">
-        <v>7.61</v>
+        <v>7.84</v>
       </c>
       <c r="S9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="T9" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="U9" t="n">
         <v>0.11</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>51.11</v>
+        <v>50.84</v>
       </c>
       <c r="Y9" t="n">
         <v>0.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.78</v>
+        <v>13.53</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.890000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.89</v>
+        <v>4.79</v>
       </c>
       <c r="AC9" t="n">
-        <v>20.17</v>
+        <v>20.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AF9" t="n">
         <v>0.28</v>
@@ -4371,70 +4371,70 @@
         <v>1.28</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.75</v>
+        <v>9.73</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="BJ9" t="n">
         <v>0.86</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM9" t="n">
         <v>0.89</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.64</v>
+        <v>4.65</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.03</v>
+        <v>5</v>
       </c>
       <c r="BR9" t="n">
-        <v>94.44</v>
+        <v>94.59</v>
       </c>
       <c r="BS9" t="n">
-        <v>83.33</v>
+        <v>83.78</v>
       </c>
       <c r="BT9" t="n">
-        <v>61.11</v>
+        <v>62.16</v>
       </c>
       <c r="BU9" t="n">
-        <v>30.56</v>
+        <v>29.73</v>
       </c>
       <c r="BV9" t="n">
-        <v>16.67</v>
+        <v>16.22</v>
       </c>
       <c r="BW9" t="n">
-        <v>16.67</v>
+        <v>16.22</v>
       </c>
       <c r="BX9" t="n">
-        <v>66.67</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="CA9" t="n">
         <v>3.48</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="CC9" t="n">
         <v>2.29</v>
@@ -4446,25 +4446,25 @@
         <v>1.37</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CH9" t="n">
         <v>1.43</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CK9" t="n">
         <v>1.46</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CM9" t="n">
         <v>2.57</v>
@@ -4476,16 +4476,16 @@
         <v>1.27</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CR9" t="n">
         <v>1.41</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CT9" t="n">
         <v>3</v>
@@ -4494,10 +4494,10 @@
         <v>1.45</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CX9" t="n">
         <v>1.55</v>
@@ -4515,85 +4515,85 @@
         <v>1.28</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="DE9" t="n">
         <v>0.3</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="DH9" t="n">
-        <v>97.28</v>
+        <v>96.81</v>
       </c>
       <c r="DI9" t="n">
         <v>-0.03</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.97</v>
+        <v>4.92</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="DM9" t="n">
-        <v>48.11</v>
+        <v>47.73</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="DP9" t="n">
-        <v>9.609999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.64</v>
+        <v>10.57</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.06</v>
+        <v>8.16</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.22</v>
+        <v>51.08</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.58</v>
+        <v>13.46</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.73</v>
+        <v>8.65</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.86</v>
+        <v>4.81</v>
       </c>
       <c r="EA9" t="n">
-        <v>20.92</v>
+        <v>20.84</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
         <v>18</v>
       </c>
       <c r="D10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4693,139 +4693,139 @@
         <v>1.39</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AI10" t="n">
-        <v>93.89</v>
+        <v>93.16</v>
       </c>
       <c r="AJ10" t="n">
         <v>0.11</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.78</v>
+        <v>4.74</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="AN10" t="n">
-        <v>40.06</v>
+        <v>39.47</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
       <c r="AQ10" t="n">
-        <v>15.17</v>
+        <v>15.05</v>
       </c>
       <c r="AR10" t="n">
-        <v>9.5</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="AS10" t="n">
-        <v>10</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>46.94</v>
+        <v>47.16</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.11</v>
       </c>
       <c r="BA10" t="n">
-        <v>10.44</v>
+        <v>10.26</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.56</v>
+        <v>6.53</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.89</v>
+        <v>3.74</v>
       </c>
       <c r="BD10" t="n">
-        <v>23</v>
+        <v>22.89</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.890000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.78</v>
+        <v>4.73</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.06</v>
+        <v>5</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>83.33</v>
+        <v>81.08</v>
       </c>
       <c r="BT10" t="n">
-        <v>52.78</v>
+        <v>51.35</v>
       </c>
       <c r="BU10" t="n">
-        <v>19.44</v>
+        <v>18.92</v>
       </c>
       <c r="BV10" t="n">
-        <v>11.11</v>
+        <v>10.81</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.56</v>
+        <v>5.41</v>
       </c>
       <c r="BX10" t="n">
-        <v>63.89</v>
+        <v>62.16</v>
       </c>
       <c r="BY10" t="n">
         <v>2.44</v>
@@ -4834,16 +4834,16 @@
         <v>2.65</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CB10" t="n">
         <v>3.42</v>
       </c>
       <c r="CC10" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="CE10" t="n">
         <v>1.42</v>
@@ -4852,10 +4852,10 @@
         <v>3</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI10" t="n">
         <v>1.95</v>
@@ -4882,13 +4882,13 @@
         <v>2.08</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.63</v>
+        <v>3.64</v>
       </c>
       <c r="CR10" t="n">
         <v>1.47</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CT10" t="n">
         <v>2.81</v>
@@ -4912,16 +4912,16 @@
         <v>2.41</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="DE10" t="n">
         <v>0.03</v>
@@ -4930,40 +4930,40 @@
         <v>0.97</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="DH10" t="n">
-        <v>99.66</v>
+        <v>99.13</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="DK10" t="n">
-        <v>5</v>
+        <v>4.97</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="DM10" t="n">
-        <v>44.5</v>
+        <v>44.08</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.98</v>
+        <v>13.95</v>
       </c>
       <c r="DQ10" t="n">
-        <v>9.66</v>
+        <v>9.81</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.779999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="DS10" t="n">
         <v>0.14</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>48.22</v>
+        <v>48.3</v>
       </c>
       <c r="DW10" t="n">
         <v>0.06</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.92</v>
+        <v>11.78</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.39</v>
+        <v>7.35</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.53</v>
+        <v>4.44</v>
       </c>
       <c r="EA10" t="n">
-        <v>24.58</v>
+        <v>24.49</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D11" t="n">
         <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>2.89</v>
       </c>
       <c r="H11" t="n">
-        <v>104.39</v>
+        <v>101.47</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="J11" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="K11" t="n">
-        <v>4.61</v>
+        <v>4.53</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="M11" t="n">
-        <v>50.22</v>
+        <v>48.53</v>
       </c>
       <c r="N11" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="O11" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="P11" t="n">
-        <v>11.44</v>
+        <v>11.74</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.83</v>
+        <v>8.58</v>
       </c>
       <c r="R11" t="n">
-        <v>7.11</v>
+        <v>7.26</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="T11" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="U11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="V11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>46.78</v>
+        <v>46.32</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.44</v>
+        <v>12.32</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.44</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="AB11" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="AC11" t="n">
-        <v>24.11</v>
+        <v>23.84</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AF11" t="n">
         <v>0.06</v>
@@ -5177,70 +5177,70 @@
         <v>1.56</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.029999999999999</v>
+        <v>8</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BM11" t="n">
         <v>0.78</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="BO11" t="n">
         <v>1</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="BR11" t="n">
-        <v>91.67</v>
+        <v>91.89</v>
       </c>
       <c r="BS11" t="n">
-        <v>63.89</v>
+        <v>64.86</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>51.35</v>
       </c>
       <c r="BU11" t="n">
-        <v>19.44</v>
+        <v>21.62</v>
       </c>
       <c r="BV11" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BX11" t="n">
-        <v>41.67</v>
+        <v>43.24</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="CA11" t="n">
         <v>3.19</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="CC11" t="n">
         <v>2.42</v>
@@ -5249,7 +5249,7 @@
         <v>2.43</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CF11" t="n">
         <v>3.35</v>
@@ -5270,10 +5270,10 @@
         <v>1.63</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CN11" t="n">
         <v>1.71</v>
@@ -5282,10 +5282,10 @@
         <v>1.44</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.46</v>
+        <v>4.45</v>
       </c>
       <c r="CR11" t="n">
         <v>1.55</v>
@@ -5321,52 +5321,52 @@
         <v>1.47</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.81</v>
+        <v>4.78</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="DH11" t="n">
-        <v>102.98</v>
+        <v>101.51</v>
       </c>
       <c r="DI11" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.42</v>
+        <v>4.38</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="DM11" t="n">
-        <v>47.7</v>
+        <v>46.9</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.36</v>
+        <v>12.49</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.140000000000001</v>
+        <v>9</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.02</v>
+        <v>7.1</v>
       </c>
       <c r="DS11" t="n">
         <v>0.08</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>44.94</v>
+        <v>44.76</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.22</v>
+        <v>12.16</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.33</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.89</v>
+        <v>3.95</v>
       </c>
       <c r="EA11" t="n">
-        <v>22.28</v>
+        <v>22.19</v>
       </c>
       <c r="EB11" t="n">
         <v>1.39</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" t="n">
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E12" t="n">
         <v>0.06</v>
@@ -5502,106 +5502,106 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AI12" t="n">
-        <v>91.94</v>
+        <v>90.37</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="AN12" t="n">
-        <v>37.56</v>
+        <v>37.42</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10.67</v>
+        <v>10.32</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.94</v>
+        <v>13.11</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.779999999999999</v>
+        <v>8.68</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AU12" t="n">
         <v>0.89</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>48.94</v>
+        <v>49.63</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.33</v>
+        <v>10.74</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.94</v>
+        <v>7.37</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="BD12" t="n">
-        <v>23.06</v>
+        <v>22.89</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.19</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="BO12" t="n">
         <v>0.92</v>
@@ -5610,28 +5610,28 @@
         <v>4.11</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.03</v>
+        <v>4.97</v>
       </c>
       <c r="BR12" t="n">
-        <v>91.67</v>
+        <v>91.89</v>
       </c>
       <c r="BS12" t="n">
-        <v>83.33</v>
+        <v>83.78</v>
       </c>
       <c r="BT12" t="n">
-        <v>61.11</v>
+        <v>62.16</v>
       </c>
       <c r="BU12" t="n">
-        <v>19.44</v>
+        <v>21.62</v>
       </c>
       <c r="BV12" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BW12" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BX12" t="n">
-        <v>61.11</v>
+        <v>62.16</v>
       </c>
       <c r="BY12" t="n">
         <v>2.63</v>
@@ -5640,16 +5640,16 @@
         <v>2.74</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.21</v>
+        <v>3.28</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.48</v>
+        <v>3.56</v>
       </c>
       <c r="CE12" t="n">
         <v>1.5</v>
@@ -5664,40 +5664,40 @@
         <v>1.31</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CJ12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CL12" t="n">
         <v>1.97</v>
-      </c>
-      <c r="CK12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CL12" t="n">
-        <v>1.96</v>
       </c>
       <c r="CM12" t="n">
         <v>2.33</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CO12" t="n">
         <v>1.42</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.36</v>
+        <v>4.35</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CS12" t="n">
         <v>3.27</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CU12" t="n">
         <v>1.36</v>
@@ -5715,94 +5715,94 @@
         <v>1.96</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DB12" t="n">
         <v>1.46</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.72</v>
+        <v>4.7</v>
       </c>
       <c r="DE12" t="n">
         <v>0.03</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DH12" t="n">
-        <v>91.33</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="DI12" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="DM12" t="n">
-        <v>39.86</v>
+        <v>39.73</v>
       </c>
       <c r="DN12" t="n">
         <v>0.62</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.3</v>
+        <v>10.14</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.86</v>
+        <v>12.95</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.42</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>46.86</v>
+        <v>47.27</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.42</v>
+        <v>11.6</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.83</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="EA12" t="n">
-        <v>22.39</v>
+        <v>22.32</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" t="n">
         <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5902,16 +5902,16 @@
         <v>0.78</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.39</v>
+        <v>3.32</v>
       </c>
       <c r="AI13" t="n">
-        <v>115.72</v>
+        <v>115.84</v>
       </c>
       <c r="AJ13" t="n">
         <v>-0.11</v>
@@ -5923,109 +5923,109 @@
         <v>6.11</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="AN13" t="n">
-        <v>55.78</v>
+        <v>56.42</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.67</v>
+        <v>2.74</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11</v>
+        <v>10.84</v>
       </c>
       <c r="AR13" t="n">
-        <v>11.39</v>
+        <v>11.42</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.72</v>
+        <v>6.63</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>52.89</v>
+        <v>52.95</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>13.78</v>
+        <v>14.26</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.779999999999999</v>
+        <v>10.16</v>
       </c>
       <c r="BC13" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="BD13" t="n">
-        <v>24.72</v>
+        <v>24.63</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="BF13" t="n">
         <v>0.89</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.75</v>
+        <v>9.73</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.31</v>
+        <v>4.32</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.42</v>
+        <v>5.38</v>
       </c>
       <c r="BR13" t="n">
-        <v>91.67</v>
+        <v>91.89</v>
       </c>
       <c r="BS13" t="n">
-        <v>55.56</v>
+        <v>56.76</v>
       </c>
       <c r="BT13" t="n">
-        <v>38.89</v>
+        <v>40.54</v>
       </c>
       <c r="BU13" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6034,7 +6034,7 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>38.89</v>
+        <v>40.54</v>
       </c>
       <c r="BY13" t="n">
         <v>1.83</v>
@@ -6046,37 +6046,37 @@
         <v>3.36</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CD13" t="n">
         <v>2.21</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CH13" t="n">
         <v>1.35</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK13" t="n">
         <v>1.49</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CM13" t="n">
         <v>2.5</v>
@@ -6088,16 +6088,16 @@
         <v>1.36</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="CR13" t="n">
         <v>1.5</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CT13" t="n">
         <v>2.71</v>
@@ -6106,10 +6106,10 @@
         <v>1.38</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX13" t="n">
         <v>1.54</v>
@@ -6124,28 +6124,28 @@
         <v>1.92</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="DE13" t="n">
         <v>0.08</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="DH13" t="n">
-        <v>116.83</v>
+        <v>116.86</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="DJ13" t="n">
         <v>0.89</v>
@@ -6154,55 +6154,55 @@
         <v>6.14</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="DM13" t="n">
-        <v>57.42</v>
+        <v>57.7</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.11</v>
+        <v>11.02</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.25</v>
+        <v>11.27</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.36</v>
+        <v>6.32</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>52.42</v>
+        <v>52.46</v>
       </c>
       <c r="DW13" t="n">
         <v>0.03</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.64</v>
+        <v>14.86</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.5</v>
+        <v>10.68</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.14</v>
+        <v>4.19</v>
       </c>
       <c r="EA13" t="n">
-        <v>25.58</v>
+        <v>25.51</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="EC13" t="n">
         <v>0.84</v>
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" t="n">
         <v>18</v>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E14" t="n">
         <v>0.06</v>
@@ -6305,52 +6305,52 @@
         <v>1.39</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.72</v>
+        <v>2.79</v>
       </c>
       <c r="AI14" t="n">
-        <v>101.78</v>
+        <v>102.37</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AL14" t="n">
         <v>5</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="AN14" t="n">
-        <v>46.5</v>
+        <v>46.68</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.56</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="AR14" t="n">
-        <v>13.94</v>
+        <v>14.11</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.609999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="AV14" t="n">
         <v>0.11</v>
@@ -6362,82 +6362,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>51.17</v>
+        <v>51.84</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.56</v>
+        <v>11.79</v>
       </c>
       <c r="BB14" t="n">
-        <v>9</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BD14" t="n">
-        <v>22.67</v>
+        <v>22.68</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="BF14" t="n">
         <v>1.11</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.779999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BO14" t="n">
         <v>1.11</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.22</v>
+        <v>5.19</v>
       </c>
       <c r="BR14" t="n">
-        <v>88.89</v>
+        <v>89.19</v>
       </c>
       <c r="BS14" t="n">
-        <v>69.44</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>38.89</v>
+        <v>37.84</v>
       </c>
       <c r="BU14" t="n">
-        <v>22.22</v>
+        <v>21.62</v>
       </c>
       <c r="BV14" t="n">
-        <v>13.89</v>
+        <v>13.51</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.56</v>
+        <v>5.41</v>
       </c>
       <c r="BX14" t="n">
-        <v>47.22</v>
+        <v>45.95</v>
       </c>
       <c r="BY14" t="n">
         <v>2.69</v>
@@ -6449,31 +6449,31 @@
         <v>3.24</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.42</v>
+        <v>3.37</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.69</v>
+        <v>3.63</v>
       </c>
       <c r="CE14" t="n">
         <v>1.44</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CK14" t="n">
         <v>1.47</v>
@@ -6488,31 +6488,31 @@
         <v>1.95</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="CU14" t="n">
         <v>1.39</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CX14" t="n">
         <v>1.53</v>
@@ -6521,7 +6521,7 @@
         <v>1.87</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="DA14" t="n">
         <v>1.93</v>
@@ -6530,52 +6530,52 @@
         <v>1.37</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF14" t="n">
         <v>0.92</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="DH14" t="n">
-        <v>98.89</v>
+        <v>99.27</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.03</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DK14" t="n">
         <v>4.92</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="DM14" t="n">
-        <v>47.7</v>
+        <v>47.76</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="DP14" t="n">
-        <v>10.17</v>
+        <v>10.06</v>
       </c>
       <c r="DQ14" t="n">
-        <v>12.97</v>
+        <v>13.08</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.359999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="DS14" t="n">
         <v>0.16</v>
@@ -6587,25 +6587,25 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>50.58</v>
+        <v>50.94</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.84</v>
+        <v>11.95</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.609999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="DZ14" t="n">
         <v>3.22</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.78</v>
+        <v>21.81</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="EC14" t="n">
         <v>1.25</v>
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F15" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="G15" t="n">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="H15" t="n">
-        <v>94.39</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="J15" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="K15" t="n">
-        <v>4.83</v>
+        <v>4.74</v>
       </c>
       <c r="L15" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="M15" t="n">
-        <v>43.94</v>
+        <v>44.11</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="O15" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="P15" t="n">
-        <v>11.11</v>
+        <v>11.42</v>
       </c>
       <c r="Q15" t="n">
-        <v>10.72</v>
+        <v>10.47</v>
       </c>
       <c r="R15" t="n">
-        <v>8.779999999999999</v>
+        <v>8.84</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="T15" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="U15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="V15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>49.28</v>
+        <v>48.58</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.33</v>
+        <v>11.05</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.17</v>
+        <v>7</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.17</v>
+        <v>4.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>22.06</v>
+        <v>22.05</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6789,70 +6789,70 @@
         <v>1.28</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.75</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="BJ15" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.36</v>
+        <v>4.32</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.31</v>
+        <v>5.27</v>
       </c>
       <c r="BR15" t="n">
-        <v>94.44</v>
+        <v>94.59</v>
       </c>
       <c r="BS15" t="n">
-        <v>69.44</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>47.22</v>
+        <v>45.95</v>
       </c>
       <c r="BU15" t="n">
-        <v>22.22</v>
+        <v>21.62</v>
       </c>
       <c r="BV15" t="n">
-        <v>11.11</v>
+        <v>10.81</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.33</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="BX15" t="n">
-        <v>47.22</v>
+        <v>45.95</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.41</v>
+        <v>3.38</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="CC15" t="n">
         <v>3.9</v>
@@ -6861,22 +6861,22 @@
         <v>4.18</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI15" t="n">
         <v>1.9</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CK15" t="n">
         <v>1.49</v>
@@ -6897,25 +6897,25 @@
         <v>2.09</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="CR15" t="n">
         <v>1.46</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CU15" t="n">
         <v>1.4</v>
       </c>
       <c r="CV15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CW15" t="n">
         <v>1.94</v>
-      </c>
-      <c r="CW15" t="n">
-        <v>1.95</v>
       </c>
       <c r="CX15" t="n">
         <v>1.56</v>
@@ -6933,52 +6933,52 @@
         <v>1.37</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="DD15" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="DE15" t="n">
         <v>0.03</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="DH15" t="n">
-        <v>93.25</v>
+        <v>92.97</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.61</v>
+        <v>4.57</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="DM15" t="n">
-        <v>44.16</v>
+        <v>44.25</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.64</v>
+        <v>11.78</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.5</v>
+        <v>10.38</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.24</v>
       </c>
       <c r="DS15" t="n">
         <v>0.03</v>
@@ -6990,25 +6990,25 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>50.5</v>
+        <v>50.11</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.5</v>
+        <v>10.38</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.11</v>
+        <v>7.03</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.72</v>
+        <v>21.73</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="EC15" t="n">
         <v>1.22</v>
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" t="n">
         <v>18</v>
       </c>
       <c r="D16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E16" t="n">
         <v>0.11</v>
@@ -7111,139 +7111,139 @@
         <v>1.22</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AG16" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>86.11</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>35.05</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>48.74</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>22.58</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BL16" t="n">
         <v>0.89</v>
       </c>
-      <c r="AH16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>87</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="AM16" t="n">
+      <c r="BM16" t="n">
         <v>0.78</v>
       </c>
-      <c r="AN16" t="n">
-        <v>36.33</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>11.44</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>9.17</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>7.72</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>22.83</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>9.390000000000001</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>0.8100000000000001</v>
-      </c>
       <c r="BN16" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.5</v>
+        <v>4.49</v>
       </c>
       <c r="BQ16" t="n">
         <v>4.86</v>
       </c>
       <c r="BR16" t="n">
-        <v>94.44</v>
+        <v>91.89</v>
       </c>
       <c r="BS16" t="n">
-        <v>63.89</v>
+        <v>62.16</v>
       </c>
       <c r="BT16" t="n">
-        <v>44.44</v>
+        <v>43.24</v>
       </c>
       <c r="BU16" t="n">
-        <v>27.78</v>
+        <v>27.03</v>
       </c>
       <c r="BV16" t="n">
-        <v>11.11</v>
+        <v>10.81</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>38.89</v>
+        <v>37.84</v>
       </c>
       <c r="BY16" t="n">
         <v>2.92</v>
@@ -7252,22 +7252,22 @@
         <v>3.07</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.29</v>
+        <v>3.31</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="CC16" t="n">
-        <v>3.47</v>
+        <v>3.57</v>
       </c>
       <c r="CD16" t="n">
-        <v>3.65</v>
+        <v>3.77</v>
       </c>
       <c r="CE16" t="n">
         <v>1.43</v>
       </c>
       <c r="CF16" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CG16" t="n">
         <v>2.72</v>
@@ -7282,7 +7282,7 @@
         <v>1.85</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CL16" t="n">
         <v>1.95</v>
@@ -7294,19 +7294,19 @@
         <v>1.87</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="CR16" t="n">
         <v>1.48</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CT16" t="n">
         <v>2.78</v>
@@ -7321,13 +7321,13 @@
         <v>1.94</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY16" t="n">
         <v>1.92</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="DA16" t="n">
         <v>1.88</v>
@@ -7339,82 +7339,82 @@
         <v>2.15</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="DE16" t="n">
         <v>0.14</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="DH16" t="n">
-        <v>93.39</v>
+        <v>92.76000000000001</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.44</v>
+        <v>4.35</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="DM16" t="n">
-        <v>42.16</v>
+        <v>41.35</v>
       </c>
       <c r="DN16" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.69</v>
+        <v>11.81</v>
       </c>
       <c r="DQ16" t="n">
-        <v>10.83</v>
+        <v>10.86</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.029999999999999</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.53</v>
+        <v>51.08</v>
       </c>
       <c r="DW16" t="n">
         <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.3</v>
+        <v>12.08</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.33</v>
+        <v>8.19</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.97</v>
+        <v>3.89</v>
       </c>
       <c r="EA16" t="n">
-        <v>22.58</v>
+        <v>22.46</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="17">
@@ -7424,61 +7424,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D17" t="n">
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="G17" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="H17" t="n">
-        <v>90.17</v>
+        <v>90.26000000000001</v>
       </c>
       <c r="I17" t="n">
         <v>-0.11</v>
       </c>
       <c r="J17" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="K17" t="n">
-        <v>5.22</v>
+        <v>5.26</v>
       </c>
       <c r="L17" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="M17" t="n">
-        <v>43</v>
+        <v>43.16</v>
       </c>
       <c r="N17" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="O17" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="P17" t="n">
-        <v>12</v>
+        <v>12.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>10.61</v>
+        <v>10.74</v>
       </c>
       <c r="R17" t="n">
-        <v>6.94</v>
+        <v>6.89</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="T17" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7490,28 +7490,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>46.17</v>
+        <v>46.63</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="Z17" t="n">
-        <v>11.28</v>
+        <v>11.26</v>
       </c>
       <c r="AA17" t="n">
         <v>8.109999999999999</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="AC17" t="n">
-        <v>22.06</v>
+        <v>22.11</v>
       </c>
       <c r="AD17" t="n">
         <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF17" t="n">
         <v>0.06</v>
@@ -7595,70 +7595,70 @@
         <v>1.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.56</v>
+        <v>9.57</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.28</v>
+        <v>4.27</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.25</v>
+        <v>5.24</v>
       </c>
       <c r="BR17" t="n">
-        <v>77.78</v>
+        <v>78.38</v>
       </c>
       <c r="BS17" t="n">
-        <v>36.11</v>
+        <v>35.14</v>
       </c>
       <c r="BT17" t="n">
-        <v>27.78</v>
+        <v>27.03</v>
       </c>
       <c r="BU17" t="n">
-        <v>13.89</v>
+        <v>13.51</v>
       </c>
       <c r="BV17" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BW17" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BX17" t="n">
-        <v>16.67</v>
+        <v>16.22</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.99</v>
+        <v>3.11</v>
       </c>
       <c r="CA17" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CC17" t="n">
         <v>3.53</v>
@@ -7667,13 +7667,13 @@
         <v>3.64</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CH17" t="n">
         <v>1.26</v>
@@ -7691,19 +7691,19 @@
         <v>2.01</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CN17" t="n">
         <v>1.81</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CQ17" t="n">
-        <v>5.15</v>
+        <v>5.13</v>
       </c>
       <c r="CR17" t="n">
         <v>1.61</v>
@@ -7712,7 +7712,7 @@
         <v>3.34</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CU17" t="n">
         <v>1.34</v>
@@ -7736,55 +7736,55 @@
         <v>1.77</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="DC17" t="n">
         <v>2.73</v>
       </c>
       <c r="DD17" t="n">
-        <v>5.53</v>
+        <v>5.51</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DH17" t="n">
-        <v>92.5</v>
+        <v>92.48</v>
       </c>
       <c r="DI17" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.36</v>
+        <v>4.4</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="DM17" t="n">
-        <v>42.94</v>
+        <v>43.03</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DP17" t="n">
         <v>13.08</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.8</v>
+        <v>10.87</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.78</v>
+        <v>6.75</v>
       </c>
       <c r="DS17" t="n">
         <v>0.03</v>
@@ -7796,28 +7796,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>47.08</v>
+        <v>47.3</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX17" t="n">
-        <v>9.609999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.86</v>
+        <v>6.89</v>
       </c>
       <c r="DZ17" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="EA17" t="n">
-        <v>22.22</v>
+        <v>22.25</v>
       </c>
       <c r="EB17" t="n">
         <v>1.12</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18" t="n">
         <v>18</v>
       </c>
       <c r="D18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E18" t="n">
         <v>0.17</v>
@@ -7920,46 +7920,46 @@
         <v>0.11</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AI18" t="n">
-        <v>92.83</v>
+        <v>92.79000000000001</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-0.22</v>
+        <v>-0.26</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.56</v>
+        <v>4.53</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="AN18" t="n">
-        <v>40.39</v>
+        <v>40.32</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.5</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="AR18" t="n">
-        <v>9.390000000000001</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="AS18" t="n">
-        <v>9.44</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AU18" t="n">
         <v>0.89</v>
@@ -7974,82 +7974,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>51.11</v>
+        <v>51.63</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="BA18" t="n">
-        <v>11.61</v>
+        <v>11.58</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.44</v>
+        <v>7.37</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.17</v>
+        <v>4.21</v>
       </c>
       <c r="BD18" t="n">
-        <v>21.06</v>
+        <v>21.53</v>
       </c>
       <c r="BE18" t="n">
         <v>1.32</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.69</v>
+        <v>10.54</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.44</v>
+        <v>4.38</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.22</v>
+        <v>6.14</v>
       </c>
       <c r="BR18" t="n">
-        <v>83.33</v>
+        <v>83.78</v>
       </c>
       <c r="BS18" t="n">
-        <v>61.11</v>
+        <v>59.46</v>
       </c>
       <c r="BT18" t="n">
-        <v>41.67</v>
+        <v>40.54</v>
       </c>
       <c r="BU18" t="n">
-        <v>19.44</v>
+        <v>18.92</v>
       </c>
       <c r="BV18" t="n">
-        <v>11.11</v>
+        <v>10.81</v>
       </c>
       <c r="BW18" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BX18" t="n">
-        <v>47.22</v>
+        <v>45.95</v>
       </c>
       <c r="BY18" t="n">
         <v>2.19</v>
@@ -8064,10 +8064,10 @@
         <v>3.4</v>
       </c>
       <c r="CC18" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.12</v>
+        <v>3.09</v>
       </c>
       <c r="CE18" t="n">
         <v>1.46</v>
@@ -8112,13 +8112,13 @@
         <v>1.48</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CT18" t="n">
         <v>2.75</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CV18" t="n">
         <v>1.96</v>
@@ -8145,49 +8145,49 @@
         <v>2.2</v>
       </c>
       <c r="DD18" t="n">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="DE18" t="n">
         <v>0.14</v>
       </c>
       <c r="DF18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="DH18" t="n">
-        <v>93.3</v>
+        <v>93.27</v>
       </c>
       <c r="DI18" t="n">
-        <v>-0.16</v>
+        <v>-0.19</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.78</v>
+        <v>4.76</v>
       </c>
       <c r="DL18" t="n">
         <v>0.38</v>
       </c>
       <c r="DM18" t="n">
-        <v>41.72</v>
+        <v>41.65</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DO18" t="n">
         <v>2.11</v>
       </c>
       <c r="DP18" t="n">
-        <v>9.109999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DQ18" t="n">
-        <v>9.390000000000001</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.5</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DS18" t="n">
         <v>0</v>
@@ -8199,28 +8199,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>51.3</v>
+        <v>51.57</v>
       </c>
       <c r="DW18" t="n">
         <v>0.03</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.14</v>
+        <v>12.11</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.140000000000001</v>
+        <v>8.08</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="EA18" t="n">
-        <v>21.83</v>
+        <v>22.06</v>
       </c>
       <c r="EB18" t="n">
         <v>1.35</v>
       </c>
       <c r="EC18" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="19">
@@ -8230,61 +8230,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D19" t="n">
         <v>18</v>
       </c>
       <c r="E19" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F19" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="G19" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="H19" t="n">
-        <v>117.17</v>
+        <v>119.05</v>
       </c>
       <c r="I19" t="n">
         <v>-0.11</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="K19" t="n">
-        <v>6.17</v>
+        <v>6.26</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="M19" t="n">
-        <v>61.94</v>
+        <v>62.63</v>
       </c>
       <c r="N19" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="O19" t="n">
-        <v>2.72</v>
+        <v>2.79</v>
       </c>
       <c r="P19" t="n">
-        <v>8.83</v>
+        <v>9</v>
       </c>
       <c r="Q19" t="n">
-        <v>14.5</v>
+        <v>14.58</v>
       </c>
       <c r="R19" t="n">
-        <v>6.56</v>
+        <v>6.37</v>
       </c>
       <c r="S19" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="T19" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8296,28 +8296,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>55.06</v>
+        <v>55.58</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>14.11</v>
+        <v>14.37</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.720000000000001</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.39</v>
+        <v>4.42</v>
       </c>
       <c r="AC19" t="n">
-        <v>25.61</v>
+        <v>25.42</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AF19" t="n">
         <v>0.06</v>
@@ -8401,70 +8401,70 @@
         <v>1.17</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.779999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.53</v>
+        <v>4.51</v>
       </c>
       <c r="BQ19" t="n">
         <v>5.22</v>
       </c>
       <c r="BR19" t="n">
-        <v>88.89</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="BS19" t="n">
-        <v>55.56</v>
+        <v>54.05</v>
       </c>
       <c r="BT19" t="n">
-        <v>41.67</v>
+        <v>40.54</v>
       </c>
       <c r="BU19" t="n">
-        <v>22.22</v>
+        <v>21.62</v>
       </c>
       <c r="BV19" t="n">
-        <v>5.56</v>
+        <v>5.41</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>44.44</v>
+        <v>43.24</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="CC19" t="n">
         <v>2.21</v>
@@ -8473,13 +8473,13 @@
         <v>2.3</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CH19" t="n">
         <v>1.34</v>
@@ -8491,7 +8491,7 @@
         <v>1.97</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL19" t="n">
         <v>1.95</v>
@@ -8506,19 +8506,19 @@
         <v>1.38</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CQ19" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CU19" t="n">
         <v>1.38</v>
@@ -8545,22 +8545,22 @@
         <v>1.41</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF19" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="DG19" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="DH19" t="n">
-        <v>114.22</v>
+        <v>115.27</v>
       </c>
       <c r="DI19" t="n">
         <v>-0.06</v>
@@ -8569,28 +8569,28 @@
         <v>0.84</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.72</v>
+        <v>5.78</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="DM19" t="n">
-        <v>55.36</v>
+        <v>55.89</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="DP19" t="n">
-        <v>8.91</v>
+        <v>9</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.72</v>
+        <v>13.78</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.28</v>
+        <v>7.16</v>
       </c>
       <c r="DS19" t="n">
         <v>0.03</v>
@@ -8602,25 +8602,25 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>52.89</v>
+        <v>53.22</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>13.42</v>
+        <v>13.57</v>
       </c>
       <c r="DY19" t="n">
-        <v>9.109999999999999</v>
+        <v>9.24</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.3</v>
+        <v>4.32</v>
       </c>
       <c r="EA19" t="n">
-        <v>27.86</v>
+        <v>27.7</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="EC19" t="n">
         <v>0.84</v>
@@ -8633,61 +8633,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D20" t="n">
         <v>18</v>
       </c>
       <c r="E20" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="G20" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="H20" t="n">
-        <v>91.94</v>
+        <v>90.16</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="J20" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="K20" t="n">
-        <v>4.17</v>
+        <v>4.05</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="M20" t="n">
-        <v>48.56</v>
+        <v>48.95</v>
       </c>
       <c r="N20" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="O20" t="n">
         <v>1.89</v>
       </c>
       <c r="P20" t="n">
-        <v>11.28</v>
+        <v>11.47</v>
       </c>
       <c r="Q20" t="n">
-        <v>10.61</v>
+        <v>10.74</v>
       </c>
       <c r="R20" t="n">
-        <v>8.06</v>
+        <v>7.84</v>
       </c>
       <c r="S20" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="T20" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -8699,28 +8699,28 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>42.39</v>
+        <v>42.74</v>
       </c>
       <c r="Y20" t="n">
         <v>0.11</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.06</v>
+        <v>10.32</v>
       </c>
       <c r="AA20" t="n">
-        <v>7.56</v>
+        <v>7.84</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AC20" t="n">
-        <v>24.61</v>
+        <v>25.26</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AF20" t="n">
         <v>0.11</v>
@@ -8804,64 +8804,64 @@
         <v>1</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.83</v>
+        <v>8.76</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.83</v>
+        <v>4.78</v>
       </c>
       <c r="BR20" t="n">
-        <v>88.89</v>
+        <v>89.19</v>
       </c>
       <c r="BS20" t="n">
-        <v>55.56</v>
+        <v>54.05</v>
       </c>
       <c r="BT20" t="n">
-        <v>30.56</v>
+        <v>29.73</v>
       </c>
       <c r="BU20" t="n">
-        <v>8.33</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="BV20" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>33.33</v>
+        <v>32.43</v>
       </c>
       <c r="BY20" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.93</v>
+        <v>2.97</v>
       </c>
       <c r="CA20" t="n">
         <v>3.09</v>
@@ -8879,7 +8879,7 @@
         <v>1.55</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="CG20" t="n">
         <v>2.43</v>
@@ -8891,19 +8891,19 @@
         <v>1.72</v>
       </c>
       <c r="CJ20" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO20" t="n">
         <v>1.48</v>
@@ -8912,16 +8912,16 @@
         <v>2.45</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.77</v>
+        <v>4.75</v>
       </c>
       <c r="CR20" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CS20" t="n">
         <v>3.33</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CU20" t="n">
         <v>1.34</v>
@@ -8933,67 +8933,67 @@
         <v>2.21</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DA20" t="n">
         <v>1.73</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="DD20" t="n">
-        <v>5.17</v>
+        <v>5.14</v>
       </c>
       <c r="DE20" t="n">
         <v>0.08</v>
       </c>
       <c r="DF20" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="DH20" t="n">
-        <v>90.75</v>
+        <v>89.87</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DK20" t="n">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM20" t="n">
-        <v>41.7</v>
+        <v>42.08</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="DO20" t="n">
         <v>1.56</v>
       </c>
       <c r="DP20" t="n">
-        <v>10.58</v>
+        <v>10.7</v>
       </c>
       <c r="DQ20" t="n">
-        <v>10.84</v>
+        <v>10.9</v>
       </c>
       <c r="DR20" t="n">
-        <v>8.17</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
@@ -9005,28 +9005,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>40.75</v>
+        <v>40.97</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="DX20" t="n">
-        <v>9.17</v>
+        <v>9.33</v>
       </c>
       <c r="DY20" t="n">
-        <v>6.67</v>
+        <v>6.84</v>
       </c>
       <c r="DZ20" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="EA20" t="n">
-        <v>22.52</v>
+        <v>22.92</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="21">
@@ -9036,10 +9036,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D21" t="n">
         <v>18</v>
@@ -9048,82 +9048,82 @@
         <v>0.11</v>
       </c>
       <c r="F21" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="G21" t="n">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="H21" t="n">
-        <v>81.28</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="J21" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="K21" t="n">
-        <v>4.56</v>
+        <v>4.53</v>
       </c>
       <c r="L21" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="M21" t="n">
-        <v>39.17</v>
+        <v>39.42</v>
       </c>
       <c r="N21" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="O21" t="n">
-        <v>2.33</v>
+        <v>2.16</v>
       </c>
       <c r="P21" t="n">
-        <v>10.94</v>
+        <v>11.32</v>
       </c>
       <c r="Q21" t="n">
-        <v>12.61</v>
+        <v>12.58</v>
       </c>
       <c r="R21" t="n">
-        <v>8.67</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="S21" t="n">
         <v>1.11</v>
       </c>
       <c r="T21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>48.95</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.22</v>
       </c>
-      <c r="U21" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>49.56</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>11.17</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>7.78</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>22.44</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9207,70 +9207,70 @@
         <v>1.78</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="BH21" t="n">
         <v>10.14</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="BO21" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.72</v>
+        <v>4.57</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.39</v>
+        <v>5.22</v>
       </c>
       <c r="BR21" t="n">
-        <v>91.67</v>
+        <v>91.89</v>
       </c>
       <c r="BS21" t="n">
-        <v>66.67</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="BT21" t="n">
-        <v>47.22</v>
+        <v>48.65</v>
       </c>
       <c r="BU21" t="n">
-        <v>22.22</v>
+        <v>24.32</v>
       </c>
       <c r="BV21" t="n">
-        <v>8.33</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="BW21" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BX21" t="n">
-        <v>33.33</v>
+        <v>35.14</v>
       </c>
       <c r="BY21" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="BZ21" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CA21" t="n">
         <v>3.43</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="CC21" t="n">
         <v>3.55</v>
@@ -9279,31 +9279,31 @@
         <v>3.82</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CI21" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CK21" t="n">
         <v>1.42</v>
       </c>
       <c r="CL21" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CN21" t="n">
         <v>2.01</v>
@@ -9312,16 +9312,16 @@
         <v>1.26</v>
       </c>
       <c r="CP21" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CR21" t="n">
         <v>1.41</v>
       </c>
       <c r="CS21" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CT21" t="n">
         <v>3.04</v>
@@ -9330,10 +9330,10 @@
         <v>1.45</v>
       </c>
       <c r="CV21" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="CW21" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CX21" t="n">
         <v>1.54</v>
@@ -9348,88 +9348,88 @@
         <v>2</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DC21" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="DD21" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="DE21" t="n">
         <v>0.06</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="DH21" t="n">
-        <v>84.22</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="DI21" t="n">
         <v>0.03</v>
       </c>
       <c r="DJ21" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="DK21" t="n">
         <v>4.22</v>
       </c>
       <c r="DL21" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DM21" t="n">
+        <v>40.78</v>
+      </c>
+      <c r="DN21" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="DO21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DP21" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="DQ21" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="DR21" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="DS21" t="n">
         <v>0.11</v>
       </c>
-      <c r="DM21" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="DN21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DO21" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="DP21" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="DQ21" t="n">
-        <v>12.58</v>
-      </c>
-      <c r="DR21" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="DS21" t="n">
-        <v>0.12</v>
-      </c>
       <c r="DT21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>49.17</v>
+        <v>48.87</v>
       </c>
       <c r="DW21" t="n">
         <v>0.03</v>
       </c>
       <c r="DX21" t="n">
-        <v>10.78</v>
+        <v>10.84</v>
       </c>
       <c r="DY21" t="n">
-        <v>7.56</v>
+        <v>7.46</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="EA21" t="n">
-        <v>20.72</v>
+        <v>20.92</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="EC21" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Japan_J1_League_2025.xlsx
+++ b/data/teams/leagues/Averages_Japan_J1_League_2025.xlsx
@@ -2341,10 +2341,10 @@
         <v>12.74</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.89</v>
+        <v>7.84</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.84</v>
+        <v>4.89</v>
       </c>
       <c r="BD4" t="n">
         <v>21.63</v>
@@ -2566,10 +2566,10 @@
         <v>13.89</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.890000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5</v>
+        <v>5.03</v>
       </c>
       <c r="EA4" t="n">
         <v>20.7</v>

--- a/data/teams/leagues/Averages_Japan_J1_League_2025.xlsx
+++ b/data/teams/leagues/Averages_Japan_J1_League_2025.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C2" t="n">
         <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
         <v>0.05</v>
@@ -1469,52 +1469,52 @@
         <v>1.16</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="AI2" t="n">
-        <v>85.39</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="AN2" t="n">
-        <v>37.5</v>
+        <v>37.16</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.109999999999999</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="AS2" t="n">
-        <v>9</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="AV2" t="n">
         <v>0.11</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>53.56</v>
+        <v>53.11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="BA2" t="n">
-        <v>10.56</v>
+        <v>10.63</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.56</v>
+        <v>7.63</v>
       </c>
       <c r="BC2" t="n">
         <v>3</v>
       </c>
       <c r="BD2" t="n">
-        <v>20.78</v>
+        <v>20.42</v>
       </c>
       <c r="BE2" t="n">
         <v>1.15</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.050000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="BJ2" t="n">
         <v>0.68</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.65</v>
+        <v>4.74</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.41</v>
+        <v>4.37</v>
       </c>
       <c r="BR2" t="n">
-        <v>94.59</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>70.27</v>
+        <v>71.05</v>
       </c>
       <c r="BT2" t="n">
-        <v>51.35</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
-        <v>32.43</v>
+        <v>31.58</v>
       </c>
       <c r="BV2" t="n">
-        <v>13.51</v>
+        <v>13.16</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.109999999999999</v>
+        <v>7.89</v>
       </c>
       <c r="BX2" t="n">
-        <v>59.46</v>
+        <v>60.53</v>
       </c>
       <c r="BY2" t="n">
         <v>3.04</v>
@@ -1613,13 +1613,13 @@
         <v>3.27</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.89</v>
+        <v>3.96</v>
       </c>
       <c r="CE2" t="n">
         <v>1.46</v>
@@ -1631,10 +1631,10 @@
         <v>2.67</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.89</v>
@@ -1643,7 +1643,7 @@
         <v>1.51</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CM2" t="n">
         <v>2.31</v>
@@ -1652,31 +1652,31 @@
         <v>1.79</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.97</v>
+        <v>3.95</v>
       </c>
       <c r="CR2" t="n">
         <v>1.5</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CU2" t="n">
         <v>1.39</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CX2" t="n">
         <v>1.62</v>
@@ -1694,52 +1694,52 @@
         <v>1.39</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="DH2" t="n">
-        <v>91.76000000000001</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="DI2" t="n">
         <v>-0.14</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.57</v>
+        <v>4.56</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="DM2" t="n">
-        <v>40.22</v>
+        <v>39.98</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="DO2" t="n">
         <v>2.1</v>
       </c>
       <c r="DP2" t="n">
-        <v>9.619999999999999</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DQ2" t="n">
-        <v>8.67</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.35</v>
+        <v>8.4</v>
       </c>
       <c r="DS2" t="n">
         <v>0.08</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>54.46</v>
+        <v>54.22</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DX2" t="n">
         <v>11.6</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.359999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DZ2" t="n">
         <v>3.24</v>
       </c>
       <c r="EA2" t="n">
-        <v>20.06</v>
+        <v>19.9</v>
       </c>
       <c r="EB2" t="n">
         <v>1.25</v>
       </c>
       <c r="EC2" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C3" t="n">
         <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
         <v>0.11</v>
@@ -1872,139 +1872,139 @@
         <v>1.32</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AI3" t="n">
-        <v>97.33</v>
+        <v>97.47</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.89</v>
+        <v>3.95</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AN3" t="n">
-        <v>46.39</v>
+        <v>46.79</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.67</v>
+        <v>12.79</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.779999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.220000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="AT3" t="n">
         <v>1</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>48.5</v>
+        <v>48.58</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.11</v>
       </c>
       <c r="BA3" t="n">
-        <v>12.44</v>
+        <v>12.37</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.17</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.5</v>
+        <v>19.58</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.029999999999999</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="BK3" t="n">
         <v>0.32</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BN3" t="n">
         <v>1.11</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="BR3" t="n">
-        <v>81.08</v>
+        <v>81.58</v>
       </c>
       <c r="BS3" t="n">
-        <v>45.95</v>
+        <v>44.74</v>
       </c>
       <c r="BT3" t="n">
-        <v>32.43</v>
+        <v>31.58</v>
       </c>
       <c r="BU3" t="n">
-        <v>16.22</v>
+        <v>15.79</v>
       </c>
       <c r="BV3" t="n">
-        <v>8.109999999999999</v>
+        <v>7.89</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.41</v>
+        <v>5.26</v>
       </c>
       <c r="BX3" t="n">
-        <v>40.54</v>
+        <v>39.47</v>
       </c>
       <c r="BY3" t="n">
         <v>2.7</v>
@@ -2013,25 +2013,25 @@
         <v>2.88</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CE3" t="n">
         <v>1.56</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CH3" t="n">
         <v>1.27</v>
@@ -2040,13 +2040,13 @@
         <v>1.7</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CM3" t="n">
         <v>2.11</v>
@@ -2055,13 +2055,13 @@
         <v>1.68</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CQ3" t="n">
-        <v>4.94</v>
+        <v>4.91</v>
       </c>
       <c r="CR3" t="n">
         <v>1.59</v>
@@ -2082,7 +2082,7 @@
         <v>2.2</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CY3" t="n">
         <v>2.18</v>
@@ -2097,13 +2097,13 @@
         <v>1.53</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="DD3" t="n">
-        <v>5.37</v>
+        <v>5.36</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF3" t="n">
         <v>0.89</v>
@@ -2112,37 +2112,37 @@
         <v>2.08</v>
       </c>
       <c r="DH3" t="n">
-        <v>93.86</v>
+        <v>94.02</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.11</v>
+        <v>4.14</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="DM3" t="n">
-        <v>45.89</v>
+        <v>46.1</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="DO3" t="n">
         <v>2</v>
       </c>
       <c r="DP3" t="n">
-        <v>12.65</v>
+        <v>12.71</v>
       </c>
       <c r="DQ3" t="n">
-        <v>10.89</v>
+        <v>10.79</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.65</v>
+        <v>7.72</v>
       </c>
       <c r="DS3" t="n">
         <v>0.11</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>46.38</v>
+        <v>46.48</v>
       </c>
       <c r="DW3" t="n">
         <v>0.08</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.97</v>
+        <v>12.92</v>
       </c>
       <c r="DY3" t="n">
-        <v>9</v>
+        <v>8.94</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.97</v>
+        <v>3.98</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.33</v>
+        <v>20.34</v>
       </c>
       <c r="EB3" t="n">
         <v>1.43</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
         <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="F4" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="G4" t="n">
-        <v>4.44</v>
+        <v>4.37</v>
       </c>
       <c r="H4" t="n">
-        <v>92.94</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="K4" t="n">
-        <v>7.11</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="M4" t="n">
-        <v>51.28</v>
+        <v>52.32</v>
       </c>
       <c r="N4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="O4" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="P4" t="n">
-        <v>9.33</v>
+        <v>9.74</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.61</v>
+        <v>12.68</v>
       </c>
       <c r="R4" t="n">
-        <v>8.220000000000001</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="T4" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>53.5</v>
+        <v>53.95</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.11</v>
+        <v>15.32</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.94</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.17</v>
+        <v>5.37</v>
       </c>
       <c r="AC4" t="n">
-        <v>19.72</v>
+        <v>19.84</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="AF4" t="n">
         <v>0.16</v>
@@ -2356,70 +2356,70 @@
         <v>1.21</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="BH4" t="n">
-        <v>11.03</v>
+        <v>11</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="BJ4" t="n">
         <v>0.92</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="BM4" t="n">
         <v>0.76</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6</v>
+        <v>5.97</v>
       </c>
       <c r="BR4" t="n">
-        <v>97.3</v>
+        <v>97.37</v>
       </c>
       <c r="BS4" t="n">
-        <v>86.48999999999999</v>
+        <v>86.84</v>
       </c>
       <c r="BT4" t="n">
-        <v>59.46</v>
+        <v>60.53</v>
       </c>
       <c r="BU4" t="n">
-        <v>32.43</v>
+        <v>34.21</v>
       </c>
       <c r="BV4" t="n">
-        <v>16.22</v>
+        <v>15.79</v>
       </c>
       <c r="BW4" t="n">
-        <v>10.81</v>
+        <v>10.53</v>
       </c>
       <c r="BX4" t="n">
-        <v>72.97</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="CA4" t="n">
         <v>3.41</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="CC4" t="n">
         <v>3</v>
@@ -2431,7 +2431,7 @@
         <v>1.37</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CG4" t="n">
         <v>2.97</v>
@@ -2449,7 +2449,7 @@
         <v>1.43</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CM4" t="n">
         <v>2.59</v>
@@ -2458,13 +2458,13 @@
         <v>2.01</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP4" t="n">
         <v>1.88</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CR4" t="n">
         <v>1.41</v>
@@ -2473,7 +2473,7 @@
         <v>2.85</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CU4" t="n">
         <v>1.46</v>
@@ -2497,85 +2497,85 @@
         <v>1.99</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DC4" t="n">
         <v>1.88</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF4" t="n">
         <v>0.84</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="DH4" t="n">
-        <v>95.92</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="DJ4" t="n">
         <v>1.1</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.65</v>
+        <v>5.63</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="DM4" t="n">
-        <v>50.7</v>
+        <v>51.24</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DP4" t="n">
-        <v>9</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.78</v>
+        <v>11.84</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.08</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>55.11</v>
+        <v>55.29</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.89</v>
+        <v>14.03</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.859999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.03</v>
+        <v>5.13</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.7</v>
+        <v>20.74</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="EC4" t="n">
         <v>1.08</v>
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5" t="n">
         <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
         <v>0.11</v>
@@ -2678,52 +2678,52 @@
         <v>1.05</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="AI5" t="n">
-        <v>94.28</v>
+        <v>95.42</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.5</v>
+        <v>4.58</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="AN5" t="n">
-        <v>41.72</v>
+        <v>41.58</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.39</v>
+        <v>2.21</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.94</v>
+        <v>11.32</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.33</v>
+        <v>9.32</v>
       </c>
       <c r="AS5" t="n">
-        <v>9</v>
+        <v>8.84</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>41.56</v>
+        <v>41.42</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.109999999999999</v>
+        <v>9.84</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.22</v>
+        <v>6.58</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.89</v>
+        <v>3.26</v>
       </c>
       <c r="BD5" t="n">
-        <v>25</v>
+        <v>24.68</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BG5" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.3</v>
+        <v>10.26</v>
       </c>
       <c r="BI5" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.84</v>
+        <v>4.68</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.41</v>
+        <v>5.24</v>
       </c>
       <c r="BR5" t="n">
-        <v>91.89</v>
+        <v>92.11</v>
       </c>
       <c r="BS5" t="n">
-        <v>56.76</v>
+        <v>57.89</v>
       </c>
       <c r="BT5" t="n">
-        <v>32.43</v>
+        <v>34.21</v>
       </c>
       <c r="BU5" t="n">
-        <v>10.81</v>
+        <v>10.53</v>
       </c>
       <c r="BV5" t="n">
-        <v>5.41</v>
+        <v>5.26</v>
       </c>
       <c r="BW5" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="BX5" t="n">
-        <v>40.54</v>
+        <v>42.11</v>
       </c>
       <c r="BY5" t="n">
         <v>3.04</v>
@@ -2822,40 +2822,40 @@
         <v>3.18</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.83</v>
+        <v>3.78</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="CE5" t="n">
         <v>1.49</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CH5" t="n">
         <v>1.32</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK5" t="n">
         <v>1.49</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CN5" t="n">
         <v>1.91</v>
@@ -2864,19 +2864,19 @@
         <v>1.4</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CQ5" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="CR5" t="n">
         <v>1.53</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CU5" t="n">
         <v>1.37</v>
@@ -2885,7 +2885,7 @@
         <v>1.85</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CX5" t="n">
         <v>1.55</v>
@@ -2900,88 +2900,88 @@
         <v>1.9</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DD5" t="n">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF5" t="n">
         <v>0.68</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="DH5" t="n">
-        <v>93.7</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.89</v>
+        <v>4.92</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="DM5" t="n">
-        <v>45.97</v>
+        <v>45.79</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.57</v>
+        <v>2.48</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.08</v>
+        <v>11.26</v>
       </c>
       <c r="DQ5" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="DR5" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="DR5" t="n">
-        <v>8.94</v>
-      </c>
       <c r="DS5" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>42.08</v>
+        <v>42</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.57</v>
+        <v>10.9</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.59</v>
+        <v>7.74</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.97</v>
+        <v>3.16</v>
       </c>
       <c r="EA5" t="n">
-        <v>25.11</v>
+        <v>24.95</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
         <v>19</v>
@@ -3003,82 +3003,82 @@
         <v>0.11</v>
       </c>
       <c r="F6" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="G6" t="n">
-        <v>2.61</v>
+        <v>2.68</v>
       </c>
       <c r="H6" t="n">
-        <v>105.17</v>
+        <v>108.47</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.17</v>
+        <v>-0.21</v>
       </c>
       <c r="J6" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="K6" t="n">
-        <v>4.72</v>
+        <v>4.84</v>
       </c>
       <c r="L6" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="M6" t="n">
-        <v>57.61</v>
+        <v>58.68</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="O6" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="P6" t="n">
-        <v>10.33</v>
+        <v>10.32</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.11</v>
+        <v>10.26</v>
       </c>
       <c r="R6" t="n">
-        <v>6.72</v>
+        <v>6.53</v>
       </c>
       <c r="S6" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T6" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="U6" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>51.89</v>
+        <v>52.95</v>
       </c>
       <c r="Y6" t="n">
         <v>0.11</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.06</v>
+        <v>14.16</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.779999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.28</v>
+        <v>4.53</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.39</v>
+        <v>20.95</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,64 +3162,64 @@
         <v>1.21</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.029999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.08</v>
+        <v>5.13</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.59</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>64.86</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>45.95</v>
+        <v>47.37</v>
       </c>
       <c r="BU6" t="n">
-        <v>32.43</v>
+        <v>34.21</v>
       </c>
       <c r="BV6" t="n">
-        <v>18.92</v>
+        <v>21.05</v>
       </c>
       <c r="BW6" t="n">
-        <v>10.81</v>
+        <v>10.53</v>
       </c>
       <c r="BX6" t="n">
-        <v>40.54</v>
+        <v>42.11</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="CA6" t="n">
         <v>3.28</v>
@@ -3240,7 +3240,7 @@
         <v>2.97</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CH6" t="n">
         <v>1.36</v>
@@ -3264,19 +3264,19 @@
         <v>1.86</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CT6" t="n">
         <v>2.81</v>
@@ -3294,7 +3294,7 @@
         <v>1.58</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.32</v>
@@ -3309,82 +3309,82 @@
         <v>2.15</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="DE6" t="n">
         <v>0.05</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="DH6" t="n">
-        <v>100.65</v>
+        <v>102.42</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.11</v>
+        <v>-0.13</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.86</v>
+        <v>4.92</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="DM6" t="n">
-        <v>54.22</v>
+        <v>54.84</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.54</v>
+        <v>10.53</v>
       </c>
       <c r="DQ6" t="n">
-        <v>9.699999999999999</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.4</v>
+        <v>7.29</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>52.38</v>
+        <v>52.9</v>
       </c>
       <c r="DW6" t="n">
         <v>0.08</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.19</v>
+        <v>13.26</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.890000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.3</v>
+        <v>4.43</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.89</v>
+        <v>20.68</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="7">
@@ -3394,61 +3394,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7" t="n">
         <v>19</v>
       </c>
       <c r="E7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="G7" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="H7" t="n">
-        <v>103.89</v>
+        <v>104.63</v>
       </c>
       <c r="I7" t="n">
         <v>0.11</v>
       </c>
       <c r="J7" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="K7" t="n">
-        <v>5.39</v>
+        <v>5.26</v>
       </c>
       <c r="L7" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="M7" t="n">
-        <v>48.89</v>
+        <v>48.84</v>
       </c>
       <c r="N7" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="O7" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="P7" t="n">
-        <v>10.17</v>
+        <v>10.21</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.33</v>
+        <v>12.58</v>
       </c>
       <c r="R7" t="n">
-        <v>8.33</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="T7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U7" t="n">
         <v>0.11</v>
@@ -3460,28 +3460,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>52.5</v>
+        <v>53.42</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>12.83</v>
+        <v>12.68</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.109999999999999</v>
+        <v>8</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.72</v>
+        <v>4.68</v>
       </c>
       <c r="AC7" t="n">
-        <v>24.72</v>
+        <v>24.79</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AF7" t="n">
         <v>0.16</v>
@@ -3565,70 +3565,70 @@
         <v>1.16</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.949999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BJ7" t="n">
         <v>0.68</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="BO7" t="n">
         <v>1.08</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.32</v>
+        <v>4.24</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.54</v>
+        <v>5.45</v>
       </c>
       <c r="BR7" t="n">
-        <v>94.59</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>62.16</v>
+        <v>63.16</v>
       </c>
       <c r="BT7" t="n">
-        <v>45.95</v>
+        <v>47.37</v>
       </c>
       <c r="BU7" t="n">
-        <v>18.92</v>
+        <v>18.42</v>
       </c>
       <c r="BV7" t="n">
-        <v>5.41</v>
+        <v>5.26</v>
       </c>
       <c r="BW7" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="BX7" t="n">
-        <v>48.65</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.45</v>
+        <v>3.49</v>
       </c>
       <c r="CC7" t="n">
         <v>2.68</v>
@@ -3640,13 +3640,13 @@
         <v>1.43</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI7" t="n">
         <v>1.9</v>
@@ -3667,22 +3667,22 @@
         <v>1.89</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.81</v>
+        <v>3.78</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="CU7" t="n">
         <v>1.41</v>
@@ -3700,19 +3700,19 @@
         <v>1.91</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DB7" t="n">
         <v>1.37</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="DE7" t="n">
         <v>0.16</v>
@@ -3721,40 +3721,40 @@
         <v>0.89</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="DH7" t="n">
-        <v>98.89</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.08</v>
+        <v>5.02</v>
       </c>
       <c r="DL7" t="n">
         <v>0.32</v>
       </c>
       <c r="DM7" t="n">
-        <v>45.27</v>
+        <v>45.34</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="DP7" t="n">
         <v>10.79</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.32</v>
+        <v>12.45</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.32</v>
+        <v>8.18</v>
       </c>
       <c r="DS7" t="n">
         <v>0.14</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>51.57</v>
+        <v>52.05</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.05</v>
+        <v>12</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.81</v>
+        <v>7.76</v>
       </c>
       <c r="DZ7" t="n">
         <v>4.24</v>
       </c>
       <c r="EA7" t="n">
-        <v>23.62</v>
+        <v>23.68</v>
       </c>
       <c r="EB7" t="n">
         <v>1.39</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="8">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
         <v>19</v>
@@ -3809,13 +3809,13 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="G8" t="n">
-        <v>3.33</v>
+        <v>3.26</v>
       </c>
       <c r="H8" t="n">
-        <v>111.22</v>
+        <v>111.42</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -3824,64 +3824,64 @@
         <v>1.11</v>
       </c>
       <c r="K8" t="n">
-        <v>5.94</v>
+        <v>5.89</v>
       </c>
       <c r="L8" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="M8" t="n">
-        <v>56.28</v>
+        <v>55.42</v>
       </c>
       <c r="N8" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="O8" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="P8" t="n">
-        <v>9.83</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.890000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>7.78</v>
+        <v>7.63</v>
       </c>
       <c r="S8" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="T8" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="U8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="V8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>62.56</v>
+        <v>62.37</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.78</v>
+        <v>12.63</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.67</v>
+        <v>8.58</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.11</v>
+        <v>4.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>22.61</v>
+        <v>23.47</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AE8" t="n">
         <v>1.11</v>
@@ -3968,70 +3968,70 @@
         <v>1.26</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.19</v>
+        <v>10.24</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.3</v>
+        <v>4.34</v>
       </c>
       <c r="BQ8" t="n">
         <v>5.89</v>
       </c>
       <c r="BR8" t="n">
-        <v>91.89</v>
+        <v>92.11</v>
       </c>
       <c r="BS8" t="n">
-        <v>72.97</v>
+        <v>71.05</v>
       </c>
       <c r="BT8" t="n">
-        <v>37.84</v>
+        <v>36.84</v>
       </c>
       <c r="BU8" t="n">
-        <v>21.62</v>
+        <v>21.05</v>
       </c>
       <c r="BV8" t="n">
-        <v>13.51</v>
+        <v>13.16</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.109999999999999</v>
+        <v>7.89</v>
       </c>
       <c r="BX8" t="n">
-        <v>48.65</v>
+        <v>47.37</v>
       </c>
       <c r="BY8" t="n">
         <v>2.13</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="CA8" t="n">
         <v>3.28</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="CC8" t="n">
         <v>2.58</v>
@@ -4061,13 +4061,13 @@
         <v>1.47</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CO8" t="n">
         <v>1.37</v>
@@ -4076,7 +4076,7 @@
         <v>2.14</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="CR8" t="n">
         <v>1.5</v>
@@ -4103,61 +4103,61 @@
         <v>1.91</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DB8" t="n">
         <v>1.39</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF8" t="n">
         <v>0.71</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="DH8" t="n">
-        <v>108.43</v>
+        <v>108.6</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.38</v>
+        <v>5.36</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="DM8" t="n">
-        <v>52.38</v>
+        <v>52.05</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="DP8" t="n">
-        <v>10.24</v>
+        <v>10.08</v>
       </c>
       <c r="DQ8" t="n">
-        <v>8.57</v>
+        <v>8.6</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.81</v>
+        <v>7.74</v>
       </c>
       <c r="DS8" t="n">
         <v>0.05</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>60.11</v>
+        <v>60.08</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.68</v>
+        <v>12.6</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.27</v>
+        <v>8.24</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="EA8" t="n">
-        <v>22.59</v>
+        <v>23.02</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" t="n">
         <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E9" t="n">
         <v>0.32</v>
@@ -4290,139 +4290,139 @@
         <v>1.26</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AI9" t="n">
-        <v>101.89</v>
+        <v>101.63</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AL9" t="n">
-        <v>5.11</v>
+        <v>4.95</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="AN9" t="n">
-        <v>50.11</v>
+        <v>48.63</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="AQ9" t="n">
         <v>9.890000000000001</v>
       </c>
       <c r="AR9" t="n">
-        <v>9.609999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.5</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>51.33</v>
+        <v>50.79</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="BA9" t="n">
-        <v>13.39</v>
+        <v>13</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.56</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.83</v>
+        <v>4.63</v>
       </c>
       <c r="BD9" t="n">
-        <v>21.67</v>
+        <v>21.47</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.73</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.87</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.65</v>
+        <v>4.61</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="BR9" t="n">
-        <v>94.59</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>83.78</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>62.16</v>
+        <v>63.16</v>
       </c>
       <c r="BU9" t="n">
-        <v>29.73</v>
+        <v>31.58</v>
       </c>
       <c r="BV9" t="n">
-        <v>16.22</v>
+        <v>15.79</v>
       </c>
       <c r="BW9" t="n">
-        <v>16.22</v>
+        <v>15.79</v>
       </c>
       <c r="BX9" t="n">
-        <v>67.56999999999999</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="BY9" t="n">
         <v>2.02</v>
@@ -4431,31 +4431,31 @@
         <v>2.08</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="CB9" t="n">
         <v>3.7</v>
       </c>
       <c r="CC9" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CD9" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CE9" t="n">
         <v>1.37</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.7</v>
@@ -4464,7 +4464,7 @@
         <v>1.46</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CM9" t="n">
         <v>2.57</v>
@@ -4473,13 +4473,13 @@
         <v>1.97</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CR9" t="n">
         <v>1.41</v>
@@ -4494,7 +4494,7 @@
         <v>1.45</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CW9" t="n">
         <v>1.74</v>
@@ -4503,7 +4503,7 @@
         <v>1.55</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.39</v>
@@ -4518,82 +4518,82 @@
         <v>1.9</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DF9" t="n">
         <v>0.84</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="DH9" t="n">
-        <v>96.81</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.92</v>
+        <v>4.85</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DM9" t="n">
-        <v>47.73</v>
+        <v>47.05</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="DP9" t="n">
-        <v>9.67</v>
+        <v>9.68</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.57</v>
+        <v>10.55</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.16</v>
+        <v>8.15</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.08</v>
+        <v>50.82</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.46</v>
+        <v>13.26</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.65</v>
+        <v>8.56</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.81</v>
+        <v>4.71</v>
       </c>
       <c r="EA9" t="n">
-        <v>20.84</v>
+        <v>20.76</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="10">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D10" t="n">
         <v>19</v>
@@ -4615,82 +4615,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="G10" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="H10" t="n">
-        <v>105.44</v>
+        <v>104.26</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="J10" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="K10" t="n">
-        <v>5.22</v>
+        <v>5.21</v>
       </c>
       <c r="L10" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="M10" t="n">
-        <v>48.94</v>
+        <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="O10" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="P10" t="n">
-        <v>12.78</v>
+        <v>13.16</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.83</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>7.56</v>
+        <v>7.63</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="T10" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="U10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="V10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>49.5</v>
+        <v>49.16</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.39</v>
+        <v>13.37</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.220000000000001</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.17</v>
+        <v>5.32</v>
       </c>
       <c r="AC10" t="n">
-        <v>26.17</v>
+        <v>25.68</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AF10" t="n">
         <v>0.05</v>
@@ -4774,34 +4774,34 @@
         <v>1.89</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.779999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="BO10" t="n">
         <v>1.16</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.73</v>
+        <v>4.71</v>
       </c>
       <c r="BQ10" t="n">
         <v>5</v>
@@ -4810,34 +4810,34 @@
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>81.08</v>
+        <v>81.58</v>
       </c>
       <c r="BT10" t="n">
-        <v>51.35</v>
+        <v>50</v>
       </c>
       <c r="BU10" t="n">
-        <v>18.92</v>
+        <v>18.42</v>
       </c>
       <c r="BV10" t="n">
-        <v>10.81</v>
+        <v>10.53</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.41</v>
+        <v>5.26</v>
       </c>
       <c r="BX10" t="n">
-        <v>62.16</v>
+        <v>60.53</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="CA10" t="n">
         <v>3.26</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="CC10" t="n">
         <v>2.97</v>
@@ -4849,13 +4849,13 @@
         <v>1.42</v>
       </c>
       <c r="CF10" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI10" t="n">
         <v>1.95</v>
@@ -4879,7 +4879,7 @@
         <v>1.33</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CQ10" t="n">
         <v>3.64</v>
@@ -4888,10 +4888,10 @@
         <v>1.47</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CU10" t="n">
         <v>1.4</v>
@@ -4903,37 +4903,37 @@
         <v>1.87</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CY10" t="n">
         <v>1.85</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="DA10" t="n">
         <v>1.97</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="DH10" t="n">
-        <v>99.13</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="DI10" t="n">
         <v>0.03</v>
@@ -4942,58 +4942,58 @@
         <v>1.76</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.97</v>
+        <v>4.98</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="DM10" t="n">
-        <v>44.08</v>
+        <v>44.23</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.95</v>
+        <v>14.1</v>
       </c>
       <c r="DQ10" t="n">
-        <v>9.81</v>
+        <v>9.84</v>
       </c>
       <c r="DR10" t="n">
         <v>8.789999999999999</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>48.3</v>
+        <v>48.16</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.78</v>
+        <v>11.82</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.35</v>
+        <v>7.29</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.44</v>
+        <v>4.53</v>
       </c>
       <c r="EA10" t="n">
-        <v>24.49</v>
+        <v>24.28</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="EC10" t="n">
         <v>1.65</v>
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
         <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E11" t="n">
         <v>0.16</v>
@@ -5096,52 +5096,52 @@
         <v>1.42</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="AI11" t="n">
-        <v>101.56</v>
+        <v>101.95</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.22</v>
+        <v>4.37</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="AN11" t="n">
-        <v>45.17</v>
+        <v>45.58</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AP11" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.28</v>
+        <v>13.11</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.44</v>
+        <v>9.16</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.94</v>
+        <v>6.95</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5153,82 +5153,82 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>43.11</v>
+        <v>43</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>12</v>
+        <v>11.84</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.220000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.78</v>
+        <v>3.68</v>
       </c>
       <c r="BD11" t="n">
-        <v>20.44</v>
+        <v>20.26</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="BH11" t="n">
-        <v>8</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BO11" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.51</v>
+        <v>3.58</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.46</v>
+        <v>4.5</v>
       </c>
       <c r="BR11" t="n">
-        <v>91.89</v>
+        <v>92.11</v>
       </c>
       <c r="BS11" t="n">
-        <v>64.86</v>
+        <v>63.16</v>
       </c>
       <c r="BT11" t="n">
-        <v>51.35</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>21.62</v>
+        <v>21.05</v>
       </c>
       <c r="BV11" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="BX11" t="n">
-        <v>43.24</v>
+        <v>42.11</v>
       </c>
       <c r="BY11" t="n">
         <v>1.99</v>
@@ -5240,28 +5240,28 @@
         <v>3.19</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CD11" t="n">
-        <v>2.43</v>
+        <v>2.59</v>
       </c>
       <c r="CE11" t="n">
         <v>1.51</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CH11" t="n">
         <v>1.31</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CJ11" t="n">
         <v>2.02</v>
@@ -5270,37 +5270,37 @@
         <v>1.63</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CN11" t="n">
         <v>1.71</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="CR11" t="n">
         <v>1.55</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CU11" t="n">
         <v>1.36</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CW11" t="n">
         <v>2.13</v>
@@ -5312,7 +5312,7 @@
         <v>2.12</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DA11" t="n">
         <v>1.72</v>
@@ -5321,49 +5321,49 @@
         <v>1.47</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.78</v>
+        <v>4.74</v>
       </c>
       <c r="DE11" t="n">
         <v>0.11</v>
       </c>
       <c r="DF11" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="DH11" t="n">
-        <v>101.51</v>
+        <v>101.71</v>
       </c>
       <c r="DI11" t="n">
         <v>-0.11</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.38</v>
+        <v>4.45</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="DM11" t="n">
-        <v>46.9</v>
+        <v>47.06</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.49</v>
+        <v>12.42</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DR11" t="n">
         <v>7.1</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>44.76</v>
+        <v>44.66</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.16</v>
+        <v>12.08</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.210000000000001</v>
+        <v>8.18</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.95</v>
+        <v>3.89</v>
       </c>
       <c r="EA11" t="n">
-        <v>22.19</v>
+        <v>22.05</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="12">
@@ -5409,88 +5409,88 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D12" t="n">
         <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="G12" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H12" t="n">
-        <v>90.72</v>
+        <v>91</v>
       </c>
       <c r="I12" t="n">
         <v>-0.11</v>
       </c>
       <c r="J12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="K12" t="n">
-        <v>4.44</v>
+        <v>4.42</v>
       </c>
       <c r="L12" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="M12" t="n">
-        <v>42.17</v>
+        <v>41.47</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="O12" t="n">
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>9.94</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.78</v>
+        <v>12.84</v>
       </c>
       <c r="R12" t="n">
-        <v>8.06</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="T12" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="U12" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="V12" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>44.78</v>
+        <v>45.05</v>
       </c>
       <c r="Y12" t="n">
         <v>0.11</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.5</v>
+        <v>12.37</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.720000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.78</v>
+        <v>3.95</v>
       </c>
       <c r="AC12" t="n">
-        <v>21.72</v>
+        <v>21.74</v>
       </c>
       <c r="AD12" t="n">
         <v>1.36</v>
@@ -5580,67 +5580,67 @@
         <v>1.47</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.140000000000001</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BL12" t="n">
         <v>0.92</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="BP12" t="n">
         <v>4.11</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.97</v>
+        <v>4.95</v>
       </c>
       <c r="BR12" t="n">
-        <v>91.89</v>
+        <v>92.11</v>
       </c>
       <c r="BS12" t="n">
-        <v>83.78</v>
+        <v>81.58</v>
       </c>
       <c r="BT12" t="n">
-        <v>62.16</v>
+        <v>60.53</v>
       </c>
       <c r="BU12" t="n">
-        <v>21.62</v>
+        <v>21.05</v>
       </c>
       <c r="BV12" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="BW12" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="BX12" t="n">
-        <v>62.16</v>
+        <v>60.53</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CB12" t="n">
         <v>3.27</v>
@@ -5655,7 +5655,7 @@
         <v>1.5</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CG12" t="n">
         <v>2.5</v>
@@ -5664,19 +5664,19 @@
         <v>1.31</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK12" t="n">
         <v>1.5</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CN12" t="n">
         <v>1.8</v>
@@ -5688,7 +5688,7 @@
         <v>2.36</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.35</v>
+        <v>4.34</v>
       </c>
       <c r="CR12" t="n">
         <v>1.54</v>
@@ -5697,7 +5697,7 @@
         <v>3.27</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CU12" t="n">
         <v>1.36</v>
@@ -5709,13 +5709,13 @@
         <v>2.07</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DA12" t="n">
         <v>1.84</v>
@@ -5724,22 +5724,22 @@
         <v>1.46</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.7</v>
+        <v>4.71</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="DG12" t="n">
         <v>2</v>
       </c>
       <c r="DH12" t="n">
-        <v>90.54000000000001</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="DI12" t="n">
         <v>-0.03</v>
@@ -5751,55 +5751,55 @@
         <v>4.13</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="DM12" t="n">
-        <v>39.73</v>
+        <v>39.44</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="DO12" t="n">
         <v>2.11</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.14</v>
+        <v>10.06</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.95</v>
+        <v>12.98</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.380000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.27</v>
+        <v>47.34</v>
       </c>
       <c r="DW12" t="n">
         <v>0.05</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.6</v>
+        <v>11.56</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.029999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.57</v>
+        <v>3.66</v>
       </c>
       <c r="EA12" t="n">
         <v>22.32</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="EC12" t="n">
         <v>1.24</v>
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D13" t="n">
         <v>19</v>
@@ -5824,82 +5824,82 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="G13" t="n">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="H13" t="n">
-        <v>117.94</v>
+        <v>118</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="J13" t="n">
         <v>0.89</v>
       </c>
       <c r="K13" t="n">
-        <v>6.17</v>
+        <v>6.26</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="M13" t="n">
-        <v>59.06</v>
+        <v>60.11</v>
       </c>
       <c r="N13" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="O13" t="n">
-        <v>2.67</v>
+        <v>2.47</v>
       </c>
       <c r="P13" t="n">
-        <v>11.22</v>
+        <v>11.11</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.11</v>
+        <v>10.89</v>
       </c>
       <c r="R13" t="n">
-        <v>6</v>
+        <v>5.84</v>
       </c>
       <c r="S13" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="T13" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="U13" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="V13" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>51.94</v>
+        <v>52.21</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="Z13" t="n">
-        <v>15.5</v>
+        <v>15.53</v>
       </c>
       <c r="AA13" t="n">
-        <v>11.22</v>
+        <v>11.16</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.28</v>
+        <v>4.37</v>
       </c>
       <c r="AC13" t="n">
-        <v>26.44</v>
+        <v>26.47</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="AF13" t="n">
         <v>0.16</v>
@@ -5983,49 +5983,49 @@
         <v>0.89</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.73</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="BM13" t="n">
         <v>0.68</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.32</v>
+        <v>4.18</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.38</v>
+        <v>5.21</v>
       </c>
       <c r="BR13" t="n">
-        <v>91.89</v>
+        <v>92.11</v>
       </c>
       <c r="BS13" t="n">
-        <v>56.76</v>
+        <v>57.89</v>
       </c>
       <c r="BT13" t="n">
-        <v>40.54</v>
+        <v>42.11</v>
       </c>
       <c r="BU13" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6034,19 +6034,19 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>40.54</v>
+        <v>42.11</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="CC13" t="n">
         <v>2.13</v>
@@ -6058,13 +6058,13 @@
         <v>1.44</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI13" t="n">
         <v>1.85</v>
@@ -6073,37 +6073,37 @@
         <v>1.91</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CN13" t="n">
         <v>1.91</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="CR13" t="n">
         <v>1.5</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="CT13" t="n">
         <v>2.71</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CV13" t="n">
         <v>1.92</v>
@@ -6115,7 +6115,7 @@
         <v>1.54</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.4</v>
@@ -6127,82 +6127,82 @@
         <v>1.38</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.01</v>
+        <v>3.97</v>
       </c>
       <c r="DE13" t="n">
         <v>0.08</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.41</v>
+        <v>3.29</v>
       </c>
       <c r="DH13" t="n">
-        <v>116.86</v>
+        <v>116.92</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ13" t="n">
         <v>0.89</v>
       </c>
       <c r="DK13" t="n">
-        <v>6.14</v>
+        <v>6.18</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="DM13" t="n">
-        <v>57.7</v>
+        <v>58.26</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.71</v>
+        <v>2.61</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.02</v>
+        <v>10.98</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.27</v>
+        <v>11.16</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.32</v>
+        <v>6.24</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>52.46</v>
+        <v>52.58</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.86</v>
+        <v>14.9</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.68</v>
+        <v>10.66</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.19</v>
+        <v>4.24</v>
       </c>
       <c r="EA13" t="n">
-        <v>25.51</v>
+        <v>25.55</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="EC13" t="n">
         <v>0.84</v>
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D14" t="n">
         <v>19</v>
       </c>
       <c r="E14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F14" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="H14" t="n">
-        <v>96</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="K14" t="n">
-        <v>4.83</v>
+        <v>4.74</v>
       </c>
       <c r="L14" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="M14" t="n">
-        <v>48.89</v>
+        <v>49.16</v>
       </c>
       <c r="N14" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="P14" t="n">
-        <v>10.78</v>
+        <v>10.68</v>
       </c>
       <c r="Q14" t="n">
-        <v>12</v>
+        <v>12.32</v>
       </c>
       <c r="R14" t="n">
-        <v>10.11</v>
+        <v>10.16</v>
       </c>
       <c r="S14" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T14" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="U14" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="V14" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>50</v>
+        <v>50.58</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="Z14" t="n">
-        <v>12.11</v>
+        <v>12.37</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.220000000000001</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="AC14" t="n">
-        <v>20.89</v>
+        <v>20.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AF14" t="n">
         <v>0.05</v>
@@ -6386,67 +6386,67 @@
         <v>1.11</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.73</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="BL14" t="n">
         <v>0.68</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.46</v>
+        <v>4.32</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.19</v>
+        <v>5.03</v>
       </c>
       <c r="BR14" t="n">
-        <v>89.19</v>
+        <v>89.47</v>
       </c>
       <c r="BS14" t="n">
-        <v>67.56999999999999</v>
+        <v>68.42</v>
       </c>
       <c r="BT14" t="n">
-        <v>37.84</v>
+        <v>39.47</v>
       </c>
       <c r="BU14" t="n">
-        <v>21.62</v>
+        <v>21.05</v>
       </c>
       <c r="BV14" t="n">
-        <v>13.51</v>
+        <v>13.16</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.41</v>
+        <v>5.26</v>
       </c>
       <c r="BX14" t="n">
-        <v>45.95</v>
+        <v>47.37</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CB14" t="n">
         <v>3.42</v>
@@ -6479,13 +6479,13 @@
         <v>1.47</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO14" t="n">
         <v>1.35</v>
@@ -6494,7 +6494,7 @@
         <v>2.09</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="CR14" t="n">
         <v>1.48</v>
@@ -6509,7 +6509,7 @@
         <v>1.39</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CW14" t="n">
         <v>1.9</v>
@@ -6530,52 +6530,52 @@
         <v>1.37</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="DE14" t="n">
         <v>0.05</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.81</v>
+        <v>2.71</v>
       </c>
       <c r="DH14" t="n">
-        <v>99.27</v>
+        <v>99.52</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.92</v>
+        <v>4.87</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.41</v>
+        <v>0.37</v>
       </c>
       <c r="DM14" t="n">
-        <v>47.76</v>
+        <v>47.92</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="DP14" t="n">
-        <v>10.06</v>
+        <v>10.02</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.08</v>
+        <v>13.21</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.27</v>
+        <v>9.32</v>
       </c>
       <c r="DS14" t="n">
         <v>0.16</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>50.94</v>
+        <v>51.21</v>
       </c>
       <c r="DW14" t="n">
         <v>0.05</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.95</v>
+        <v>12.08</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.73</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.22</v>
+        <v>3.29</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.81</v>
+        <v>21.82</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
         <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E15" t="n">
         <v>0.05</v>
@@ -6711,49 +6711,49 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="AI15" t="n">
-        <v>92.11</v>
+        <v>90.63</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.39</v>
+        <v>4.53</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="AN15" t="n">
-        <v>44.39</v>
+        <v>43.58</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12.17</v>
+        <v>11.95</v>
       </c>
       <c r="AR15" t="n">
-        <v>10.28</v>
+        <v>10.21</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.61</v>
+        <v>7.74</v>
       </c>
       <c r="AT15" t="n">
         <v>1.89</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6765,82 +6765,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>51.72</v>
+        <v>51.26</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.67</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.06</v>
+        <v>6.84</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.61</v>
+        <v>2.79</v>
       </c>
       <c r="BD15" t="n">
-        <v>21.39</v>
+        <v>21.32</v>
       </c>
       <c r="BE15" t="n">
         <v>1.12</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.699999999999999</v>
+        <v>9.84</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.32</v>
+        <v>4.18</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.27</v>
+        <v>5.11</v>
       </c>
       <c r="BR15" t="n">
-        <v>94.59</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS15" t="n">
-        <v>67.56999999999999</v>
+        <v>68.42</v>
       </c>
       <c r="BT15" t="n">
-        <v>45.95</v>
+        <v>47.37</v>
       </c>
       <c r="BU15" t="n">
-        <v>21.62</v>
+        <v>21.05</v>
       </c>
       <c r="BV15" t="n">
-        <v>10.81</v>
+        <v>10.53</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.109999999999999</v>
+        <v>7.89</v>
       </c>
       <c r="BX15" t="n">
-        <v>45.95</v>
+        <v>47.37</v>
       </c>
       <c r="BY15" t="n">
         <v>3.14</v>
@@ -6849,25 +6849,25 @@
         <v>3.38</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.39</v>
+        <v>3.43</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.56</v>
+        <v>3.64</v>
       </c>
       <c r="CC15" t="n">
-        <v>3.9</v>
+        <v>4.12</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.18</v>
+        <v>4.52</v>
       </c>
       <c r="CE15" t="n">
         <v>1.43</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CH15" t="n">
         <v>1.37</v>
@@ -6876,16 +6876,16 @@
         <v>1.9</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CK15" t="n">
         <v>1.49</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CN15" t="n">
         <v>1.91</v>
@@ -6894,22 +6894,22 @@
         <v>1.34</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.76</v>
+        <v>3.72</v>
       </c>
       <c r="CR15" t="n">
         <v>1.46</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="CT15" t="n">
         <v>2.85</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CV15" t="n">
         <v>1.95</v>
@@ -6921,97 +6921,97 @@
         <v>1.56</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.38</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.97</v>
+        <v>3.92</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.57</v>
+        <v>2.48</v>
       </c>
       <c r="DH15" t="n">
-        <v>92.97</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="DI15" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.57</v>
+        <v>4.64</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DM15" t="n">
-        <v>44.25</v>
+        <v>43.85</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.78</v>
+        <v>11.68</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.38</v>
+        <v>10.34</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.24</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>50.11</v>
+        <v>49.92</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.38</v>
+        <v>10.34</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.03</v>
+        <v>6.92</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.73</v>
+        <v>21.68</v>
       </c>
       <c r="EB15" t="n">
         <v>1.22</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="16">
@@ -7021,10 +7021,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D16" t="n">
         <v>19</v>
@@ -7033,82 +7033,82 @@
         <v>0.11</v>
       </c>
       <c r="F16" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="G16" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="H16" t="n">
-        <v>99.78</v>
+        <v>101.05</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="K16" t="n">
-        <v>4.83</v>
+        <v>4.95</v>
       </c>
       <c r="L16" t="n">
-        <v>0.33</v>
+        <v>0.42</v>
       </c>
       <c r="M16" t="n">
-        <v>48</v>
+        <v>47.74</v>
       </c>
       <c r="N16" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="O16" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="P16" t="n">
-        <v>11.94</v>
+        <v>11.68</v>
       </c>
       <c r="Q16" t="n">
-        <v>11.44</v>
+        <v>11.84</v>
       </c>
       <c r="R16" t="n">
         <v>6.89</v>
       </c>
       <c r="S16" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T16" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="U16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="V16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>53.56</v>
+        <v>53.63</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>13.94</v>
+        <v>14.05</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.94</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="AB16" t="n">
-        <v>5</v>
+        <v>4.84</v>
       </c>
       <c r="AC16" t="n">
-        <v>22.33</v>
+        <v>22.32</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF16" t="n">
         <v>0.16</v>
@@ -7192,70 +7192,70 @@
         <v>1.63</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.380000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.49</v>
+        <v>4.58</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.86</v>
+        <v>4.82</v>
       </c>
       <c r="BR16" t="n">
-        <v>91.89</v>
+        <v>92.11</v>
       </c>
       <c r="BS16" t="n">
-        <v>62.16</v>
+        <v>63.16</v>
       </c>
       <c r="BT16" t="n">
-        <v>43.24</v>
+        <v>42.11</v>
       </c>
       <c r="BU16" t="n">
-        <v>27.03</v>
+        <v>26.32</v>
       </c>
       <c r="BV16" t="n">
-        <v>10.81</v>
+        <v>10.53</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>37.84</v>
+        <v>39.47</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="BZ16" t="n">
-        <v>3.07</v>
+        <v>2.99</v>
       </c>
       <c r="CA16" t="n">
         <v>3.31</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="CC16" t="n">
         <v>3.57</v>
@@ -7270,7 +7270,7 @@
         <v>2.99</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CH16" t="n">
         <v>1.37</v>
@@ -7282,10 +7282,10 @@
         <v>1.85</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CM16" t="n">
         <v>2.39</v>
@@ -7297,28 +7297,28 @@
         <v>1.34</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="CR16" t="n">
         <v>1.48</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="CU16" t="n">
         <v>1.39</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CX16" t="n">
         <v>1.56</v>
@@ -7336,10 +7336,10 @@
         <v>1.36</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="DE16" t="n">
         <v>0.14</v>
@@ -7348,40 +7348,40 @@
         <v>0.87</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="DH16" t="n">
-        <v>92.76000000000001</v>
+        <v>93.58</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.35</v>
+        <v>4.42</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="DM16" t="n">
-        <v>41.35</v>
+        <v>41.4</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.81</v>
+        <v>11.68</v>
       </c>
       <c r="DQ16" t="n">
-        <v>10.86</v>
+        <v>11.08</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.210000000000001</v>
+        <v>8.18</v>
       </c>
       <c r="DS16" t="n">
         <v>0.16</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.08</v>
+        <v>51.18</v>
       </c>
       <c r="DW16" t="n">
         <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.08</v>
+        <v>12.18</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.19</v>
+        <v>8.34</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.89</v>
+        <v>3.84</v>
       </c>
       <c r="EA16" t="n">
-        <v>22.46</v>
+        <v>22.45</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C17" t="n">
         <v>19</v>
       </c>
       <c r="D17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E17" t="n">
         <v>0.05</v>
@@ -7514,139 +7514,139 @@
         <v>1.16</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AG17" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>93.05</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>42.11</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>46.95</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BN17" t="n">
         <v>0.89</v>
       </c>
-      <c r="AH17" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>94.83</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>42.89</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>14.17</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>6.61</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>48</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>7.94</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>5.61</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>22.39</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>9.57</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>0.84</v>
-      </c>
       <c r="BO17" t="n">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.27</v>
+        <v>4.24</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.24</v>
+        <v>5.29</v>
       </c>
       <c r="BR17" t="n">
-        <v>78.38</v>
+        <v>78.95</v>
       </c>
       <c r="BS17" t="n">
-        <v>35.14</v>
+        <v>36.84</v>
       </c>
       <c r="BT17" t="n">
-        <v>27.03</v>
+        <v>28.95</v>
       </c>
       <c r="BU17" t="n">
-        <v>13.51</v>
+        <v>15.79</v>
       </c>
       <c r="BV17" t="n">
-        <v>2.7</v>
+        <v>5.26</v>
       </c>
       <c r="BW17" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="BX17" t="n">
-        <v>16.22</v>
+        <v>18.42</v>
       </c>
       <c r="BY17" t="n">
         <v>2.92</v>
@@ -7658,22 +7658,22 @@
         <v>3</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
       <c r="CE17" t="n">
         <v>1.57</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CH17" t="n">
         <v>1.26</v>
@@ -7682,7 +7682,7 @@
         <v>1.67</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CK17" t="n">
         <v>1.55</v>
@@ -7700,28 +7700,28 @@
         <v>1.51</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="CQ17" t="n">
-        <v>5.13</v>
+        <v>5.08</v>
       </c>
       <c r="CR17" t="n">
         <v>1.61</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.34</v>
+        <v>3.29</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CX17" t="n">
         <v>1.63</v>
@@ -7739,85 +7739,85 @@
         <v>1.55</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="DD17" t="n">
-        <v>5.51</v>
+        <v>5.46</v>
       </c>
       <c r="DE17" t="n">
         <v>0.05</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="DH17" t="n">
-        <v>92.48</v>
+        <v>91.66</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="DM17" t="n">
-        <v>43.03</v>
+        <v>42.64</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="DP17" t="n">
-        <v>13.08</v>
+        <v>13.1</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.87</v>
+        <v>10.84</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.75</v>
+        <v>6.68</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>47.3</v>
+        <v>46.79</v>
       </c>
       <c r="DW17" t="n">
         <v>0.05</v>
       </c>
       <c r="DX17" t="n">
-        <v>9.640000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.89</v>
+        <v>6.9</v>
       </c>
       <c r="DZ17" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="EA17" t="n">
-        <v>22.25</v>
+        <v>22</v>
       </c>
       <c r="EB17" t="n">
         <v>1.12</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="18">
@@ -7827,61 +7827,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D18" t="n">
         <v>19</v>
       </c>
       <c r="E18" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="F18" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="G18" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="H18" t="n">
-        <v>93.78</v>
+        <v>95.16</v>
       </c>
       <c r="I18" t="n">
         <v>-0.11</v>
       </c>
       <c r="J18" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="L18" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="M18" t="n">
-        <v>43.06</v>
+        <v>44.16</v>
       </c>
       <c r="N18" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="O18" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="P18" t="n">
-        <v>8.720000000000001</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>9.390000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="R18" t="n">
-        <v>9.56</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="T18" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -7893,28 +7893,28 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>51.5</v>
+        <v>51.89</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>12.67</v>
+        <v>12.89</v>
       </c>
       <c r="AA18" t="n">
-        <v>8.83</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.83</v>
+        <v>3.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>22.61</v>
+        <v>22.42</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="AF18" t="n">
         <v>0.11</v>
@@ -7998,70 +7998,70 @@
         <v>1.16</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.54</v>
+        <v>10.42</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.84</v>
+        <v>0.89</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="BO18" t="n">
         <v>0.92</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.38</v>
+        <v>4.34</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.14</v>
+        <v>6.05</v>
       </c>
       <c r="BR18" t="n">
-        <v>83.78</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>59.46</v>
+        <v>60.53</v>
       </c>
       <c r="BT18" t="n">
-        <v>40.54</v>
+        <v>42.11</v>
       </c>
       <c r="BU18" t="n">
-        <v>18.92</v>
+        <v>21.05</v>
       </c>
       <c r="BV18" t="n">
-        <v>10.81</v>
+        <v>10.53</v>
       </c>
       <c r="BW18" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="BX18" t="n">
-        <v>45.95</v>
+        <v>44.74</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="CA18" t="n">
         <v>3.26</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="CC18" t="n">
         <v>2.87</v>
@@ -8070,31 +8070,31 @@
         <v>3.09</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CL18" t="n">
         <v>1.89</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CN18" t="n">
         <v>1.89</v>
@@ -8103,10 +8103,10 @@
         <v>1.35</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="CR18" t="n">
         <v>1.48</v>
@@ -8121,16 +8121,16 @@
         <v>1.37</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CX18" t="n">
         <v>1.56</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.36</v>
@@ -8139,55 +8139,55 @@
         <v>1.89</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="DD18" t="n">
-        <v>4.01</v>
+        <v>3.97</v>
       </c>
       <c r="DE18" t="n">
         <v>0.14</v>
       </c>
       <c r="DF18" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="DH18" t="n">
-        <v>93.27</v>
+        <v>93.98</v>
       </c>
       <c r="DI18" t="n">
-        <v>-0.19</v>
+        <v>-0.18</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.76</v>
+        <v>4.74</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="DM18" t="n">
-        <v>41.65</v>
+        <v>42.24</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DP18" t="n">
-        <v>9.050000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="DQ18" t="n">
-        <v>9.460000000000001</v>
+        <v>9.48</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.539999999999999</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="DS18" t="n">
         <v>0</v>
@@ -8199,28 +8199,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>51.57</v>
+        <v>51.76</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.11</v>
+        <v>12.24</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.08</v>
+        <v>8.16</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.03</v>
+        <v>4.08</v>
       </c>
       <c r="EA18" t="n">
-        <v>22.06</v>
+        <v>21.98</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="EC18" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="19">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C19" t="n">
         <v>19</v>
       </c>
       <c r="D19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E19" t="n">
         <v>0.05</v>
@@ -8320,139 +8320,139 @@
         <v>0.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="AI19" t="n">
-        <v>111.28</v>
+        <v>111</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.28</v>
+        <v>5.21</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AN19" t="n">
-        <v>48.78</v>
+        <v>49.32</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>12.94</v>
+        <v>13.32</v>
       </c>
       <c r="AS19" t="n">
-        <v>8</v>
+        <v>7.89</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>50.72</v>
+        <v>51.05</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>12.72</v>
+        <v>12.58</v>
       </c>
       <c r="BB19" t="n">
-        <v>8.5</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.22</v>
+        <v>4.11</v>
       </c>
       <c r="BD19" t="n">
-        <v>30.11</v>
+        <v>29.84</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BG19" t="n">
         <v>2.08</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.76</v>
+        <v>9.74</v>
       </c>
       <c r="BI19" t="n">
         <v>2.08</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="BL19" t="n">
         <v>0.68</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.51</v>
+        <v>4.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.22</v>
+        <v>5.21</v>
       </c>
       <c r="BR19" t="n">
-        <v>86.48999999999999</v>
+        <v>86.84</v>
       </c>
       <c r="BS19" t="n">
-        <v>54.05</v>
+        <v>55.26</v>
       </c>
       <c r="BT19" t="n">
-        <v>40.54</v>
+        <v>39.47</v>
       </c>
       <c r="BU19" t="n">
-        <v>21.62</v>
+        <v>21.05</v>
       </c>
       <c r="BV19" t="n">
-        <v>5.41</v>
+        <v>5.26</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>43.24</v>
+        <v>42.11</v>
       </c>
       <c r="BY19" t="n">
         <v>1.9</v>
@@ -8461,13 +8461,13 @@
         <v>1.97</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CD19" t="n">
         <v>2.3</v>
@@ -8476,19 +8476,19 @@
         <v>1.47</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CG19" t="n">
         <v>2.64</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK19" t="n">
         <v>1.5</v>
@@ -8503,31 +8503,31 @@
         <v>1.89</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CQ19" t="n">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="CR19" t="n">
         <v>1.5</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CU19" t="n">
         <v>1.38</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CW19" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CX19" t="n">
         <v>1.56</v>
@@ -8536,94 +8536,94 @@
         <v>1.91</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DA19" t="n">
         <v>1.9</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.21</v>
+        <v>4.18</v>
       </c>
       <c r="DE19" t="n">
         <v>0.05</v>
       </c>
       <c r="DF19" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="DG19" t="n">
         <v>3.08</v>
       </c>
       <c r="DH19" t="n">
-        <v>115.27</v>
+        <v>115.02</v>
       </c>
       <c r="DI19" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ19" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.78</v>
+        <v>5.74</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM19" t="n">
-        <v>55.89</v>
+        <v>55.98</v>
       </c>
       <c r="DN19" t="n">
         <v>0.32</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="DP19" t="n">
-        <v>9</v>
+        <v>9.06</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.78</v>
+        <v>13.95</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.16</v>
+        <v>7.13</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>53.22</v>
+        <v>53.32</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>13.57</v>
+        <v>13.48</v>
       </c>
       <c r="DY19" t="n">
-        <v>9.24</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.32</v>
+        <v>4.26</v>
       </c>
       <c r="EA19" t="n">
-        <v>27.7</v>
+        <v>27.63</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="EC19" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="20">
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C20" t="n">
         <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E20" t="n">
         <v>0.05</v>
@@ -8726,49 +8726,49 @@
         <v>0.11</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AI20" t="n">
-        <v>89.56</v>
+        <v>89.47</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AL20" t="n">
-        <v>3.28</v>
+        <v>3.37</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="AN20" t="n">
-        <v>34.83</v>
+        <v>35.37</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9.890000000000001</v>
+        <v>10.11</v>
       </c>
       <c r="AR20" t="n">
-        <v>11.06</v>
+        <v>11.37</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.279999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.61</v>
+        <v>0.74</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
@@ -8780,82 +8780,82 @@
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>39.11</v>
+        <v>39.05</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.279999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="BB20" t="n">
-        <v>5.78</v>
+        <v>5.89</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BD20" t="n">
-        <v>20.44</v>
+        <v>20.42</v>
       </c>
       <c r="BE20" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="BF20" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.76</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="BN20" t="n">
         <v>1.24</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.59</v>
+        <v>0.66</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.89</v>
+        <v>3.92</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="BR20" t="n">
-        <v>89.19</v>
+        <v>89.47</v>
       </c>
       <c r="BS20" t="n">
-        <v>54.05</v>
+        <v>55.26</v>
       </c>
       <c r="BT20" t="n">
-        <v>29.73</v>
+        <v>31.58</v>
       </c>
       <c r="BU20" t="n">
-        <v>8.109999999999999</v>
+        <v>10.53</v>
       </c>
       <c r="BV20" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>32.43</v>
+        <v>34.21</v>
       </c>
       <c r="BY20" t="n">
         <v>2.83</v>
@@ -8864,73 +8864,73 @@
         <v>2.97</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="CC20" t="n">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="CD20" t="n">
-        <v>4.31</v>
+        <v>4.35</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="CH20" t="n">
         <v>1.28</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CJ20" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CK20" t="n">
         <v>1.6</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="CR20" t="n">
         <v>1.56</v>
       </c>
       <c r="CS20" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CW20" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CX20" t="n">
         <v>1.66</v>
@@ -8945,55 +8945,55 @@
         <v>1.73</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="DD20" t="n">
-        <v>5.14</v>
+        <v>5.08</v>
       </c>
       <c r="DE20" t="n">
         <v>0.08</v>
       </c>
       <c r="DF20" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DH20" t="n">
-        <v>89.87</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="DI20" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="DK20" t="n">
-        <v>3.68</v>
+        <v>3.71</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="DM20" t="n">
-        <v>42.08</v>
+        <v>42.16</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="DP20" t="n">
-        <v>10.7</v>
+        <v>10.79</v>
       </c>
       <c r="DQ20" t="n">
-        <v>10.9</v>
+        <v>11.06</v>
       </c>
       <c r="DR20" t="n">
-        <v>8.050000000000001</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
@@ -9005,28 +9005,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>40.97</v>
+        <v>40.9</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX20" t="n">
-        <v>9.33</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="DY20" t="n">
-        <v>6.84</v>
+        <v>6.86</v>
       </c>
       <c r="DZ20" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="EA20" t="n">
-        <v>22.92</v>
+        <v>22.84</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="21">
@@ -9036,13 +9036,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C21" t="n">
         <v>19</v>
       </c>
       <c r="D21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E21" t="n">
         <v>0.11</v>
@@ -9129,136 +9129,136 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="AI21" t="n">
-        <v>87.17</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AL21" t="n">
-        <v>3.89</v>
+        <v>3.68</v>
       </c>
       <c r="AM21" t="n">
         <v>0.11</v>
       </c>
       <c r="AN21" t="n">
-        <v>42.22</v>
+        <v>41</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11.72</v>
+        <v>12</v>
       </c>
       <c r="AR21" t="n">
-        <v>12.56</v>
+        <v>12.47</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.61</v>
+        <v>7.53</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AU21" t="n">
         <v>1.11</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>48.78</v>
+        <v>47.79</v>
       </c>
       <c r="AZ21" t="n">
         <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>10.39</v>
+        <v>10</v>
       </c>
       <c r="BB21" t="n">
-        <v>7.33</v>
+        <v>7</v>
       </c>
       <c r="BC21" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="BD21" t="n">
-        <v>19</v>
+        <v>19.16</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="BH21" t="n">
-        <v>10.14</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="BL21" t="n">
         <v>0.68</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="BO21" t="n">
         <v>1.03</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.57</v>
+        <v>4.47</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.22</v>
+        <v>5.13</v>
       </c>
       <c r="BR21" t="n">
-        <v>91.89</v>
+        <v>92.11</v>
       </c>
       <c r="BS21" t="n">
-        <v>67.56999999999999</v>
+        <v>68.42</v>
       </c>
       <c r="BT21" t="n">
-        <v>48.65</v>
+        <v>50</v>
       </c>
       <c r="BU21" t="n">
-        <v>24.32</v>
+        <v>23.68</v>
       </c>
       <c r="BV21" t="n">
-        <v>8.109999999999999</v>
+        <v>7.89</v>
       </c>
       <c r="BW21" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="BX21" t="n">
-        <v>35.14</v>
+        <v>36.84</v>
       </c>
       <c r="BY21" t="n">
         <v>2.72</v>
@@ -9267,16 +9267,16 @@
         <v>2.9</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.43</v>
+        <v>3.44</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="CC21" t="n">
-        <v>3.55</v>
+        <v>3.59</v>
       </c>
       <c r="CD21" t="n">
-        <v>3.82</v>
+        <v>3.98</v>
       </c>
       <c r="CE21" t="n">
         <v>1.36</v>
@@ -9285,7 +9285,7 @@
         <v>2.71</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CH21" t="n">
         <v>1.45</v>
@@ -9309,40 +9309,40 @@
         <v>2.01</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP21" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CR21" t="n">
         <v>1.41</v>
       </c>
       <c r="CS21" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CT21" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CU21" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CV21" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CW21" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CY21" t="n">
         <v>1.8</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="DA21" t="n">
         <v>2</v>
@@ -9354,49 +9354,49 @@
         <v>1.9</v>
       </c>
       <c r="DD21" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="DH21" t="n">
-        <v>84.34999999999999</v>
+        <v>83.97</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DJ21" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.22</v>
+        <v>4.11</v>
       </c>
       <c r="DL21" t="n">
         <v>0.08</v>
       </c>
       <c r="DM21" t="n">
-        <v>40.78</v>
+        <v>40.21</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.51</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="DP21" t="n">
-        <v>11.51</v>
+        <v>11.66</v>
       </c>
       <c r="DQ21" t="n">
-        <v>12.57</v>
+        <v>12.52</v>
       </c>
       <c r="DR21" t="n">
-        <v>8.050000000000001</v>
+        <v>8</v>
       </c>
       <c r="DS21" t="n">
         <v>0.11</v>
@@ -9408,28 +9408,28 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>48.87</v>
+        <v>48.37</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DX21" t="n">
-        <v>10.84</v>
+        <v>10.63</v>
       </c>
       <c r="DY21" t="n">
-        <v>7.46</v>
+        <v>7.29</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="EA21" t="n">
-        <v>20.92</v>
+        <v>20.95</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="EC21" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Japan_J1_League_2025.xlsx
+++ b/data/teams/leagues/Averages_Japan_J1_League_2025.xlsx
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>53.11</v>
+        <v>53.05</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.05</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>54.22</v>
+        <v>54.18</v>
       </c>
       <c r="DW2" t="n">
         <v>0.02</v>
@@ -1911,7 +1911,7 @@
         <v>9.630000000000001</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.32</v>
+        <v>8.26</v>
       </c>
       <c r="AT3" t="n">
         <v>1</v>
@@ -2142,7 +2142,7 @@
         <v>10.79</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.72</v>
+        <v>7.68</v>
       </c>
       <c r="DS3" t="n">
         <v>0.11</v>
@@ -2711,7 +2711,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.32</v>
+        <v>11.26</v>
       </c>
       <c r="AR5" t="n">
         <v>9.32</v>
@@ -2741,10 +2741,10 @@
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.84</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.58</v>
+        <v>6.53</v>
       </c>
       <c r="BC5" t="n">
         <v>3.26</v>
@@ -2753,7 +2753,7 @@
         <v>24.68</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BF5" t="n">
         <v>1.16</v>
@@ -2942,7 +2942,7 @@
         <v>2.48</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.26</v>
+        <v>11.24</v>
       </c>
       <c r="DQ5" t="n">
         <v>8.869999999999999</v>
@@ -2966,10 +2966,10 @@
         <v>0.02</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.9</v>
+        <v>10.87</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.74</v>
+        <v>7.71</v>
       </c>
       <c r="DZ5" t="n">
         <v>3.16</v>
@@ -2978,7 +2978,7 @@
         <v>24.95</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="EC5" t="n">
         <v>1.1</v>
@@ -4353,10 +4353,10 @@
         <v>0.05</v>
       </c>
       <c r="BA9" t="n">
-        <v>13</v>
+        <v>13.05</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.369999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="BC9" t="n">
         <v>4.63</v>
@@ -4578,10 +4578,10 @@
         <v>0.08</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.26</v>
+        <v>13.29</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.56</v>
+        <v>8.58</v>
       </c>
       <c r="DZ9" t="n">
         <v>4.71</v>
@@ -4651,7 +4651,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>7.63</v>
+        <v>7.58</v>
       </c>
       <c r="S10" t="n">
         <v>0.89</v>
@@ -4684,7 +4684,7 @@
         <v>5.32</v>
       </c>
       <c r="AC10" t="n">
-        <v>25.68</v>
+        <v>25.74</v>
       </c>
       <c r="AD10" t="n">
         <v>1.58</v>
@@ -4963,7 +4963,7 @@
         <v>9.84</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.789999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="DS10" t="n">
         <v>0.13</v>
@@ -4990,7 +4990,7 @@
         <v>4.53</v>
       </c>
       <c r="EA10" t="n">
-        <v>24.28</v>
+        <v>24.32</v>
       </c>
       <c r="EB10" t="n">
         <v>1.39</v>
@@ -5159,10 +5159,10 @@
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>11.84</v>
+        <v>11.89</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.16</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="BC11" t="n">
         <v>3.68</v>
@@ -5384,10 +5384,10 @@
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.08</v>
+        <v>12.1</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.18</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="DZ11" t="n">
         <v>3.89</v>
@@ -6260,7 +6260,7 @@
         <v>10.68</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.32</v>
+        <v>12.26</v>
       </c>
       <c r="R14" t="n">
         <v>10.16</v>
@@ -6296,7 +6296,7 @@
         <v>4</v>
       </c>
       <c r="AC14" t="n">
-        <v>20.95</v>
+        <v>21</v>
       </c>
       <c r="AD14" t="n">
         <v>1.42</v>
@@ -6572,7 +6572,7 @@
         <v>10.02</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.21</v>
+        <v>13.18</v>
       </c>
       <c r="DR14" t="n">
         <v>9.32</v>
@@ -6602,7 +6602,7 @@
         <v>3.29</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.82</v>
+        <v>21.84</v>
       </c>
       <c r="EB14" t="n">
         <v>1.34</v>
@@ -7087,7 +7087,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>53.63</v>
+        <v>53.68</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -7393,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.18</v>
+        <v>51.21</v>
       </c>
       <c r="DW16" t="n">
         <v>0</v>
@@ -7580,10 +7580,10 @@
         <v>8.109999999999999</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.68</v>
+        <v>5.74</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="BD17" t="n">
         <v>21.89</v>
@@ -7805,10 +7805,10 @@
         <v>9.68</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.9</v>
+        <v>6.92</v>
       </c>
       <c r="DZ17" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="EA17" t="n">
         <v>22</v>
@@ -7899,19 +7899,19 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>12.89</v>
+        <v>12.95</v>
       </c>
       <c r="AA18" t="n">
         <v>8.949999999999999</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AC18" t="n">
         <v>22.42</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE18" t="n">
         <v>0.74</v>
@@ -8205,13 +8205,13 @@
         <v>0.02</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.24</v>
+        <v>12.26</v>
       </c>
       <c r="DY18" t="n">
         <v>8.16</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.08</v>
+        <v>4.11</v>
       </c>
       <c r="EA18" t="n">
         <v>21.98</v>

--- a/data/teams/leagues/Averages_Japan_J1_League_2025.xlsx
+++ b/data/teams/leagues/Averages_Japan_J1_League_2025.xlsx
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>55.32</v>
+        <v>55.26</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>54.18</v>
+        <v>54.15</v>
       </c>
       <c r="DW2" t="n">
         <v>0.02</v>
@@ -2281,7 +2281,7 @@
         <v>0.89</v>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AI4" t="n">
         <v>98.73999999999999</v>
@@ -2296,7 +2296,7 @@
         <v>4.26</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="AN4" t="n">
         <v>50.16</v>
@@ -2305,7 +2305,7 @@
         <v>0.37</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AQ4" t="n">
         <v>8.68</v>
@@ -2383,10 +2383,10 @@
         <v>1.58</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.66</v>
+        <v>4.79</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.97</v>
+        <v>6.13</v>
       </c>
       <c r="BR4" t="n">
         <v>97.37</v>
@@ -2512,7 +2512,7 @@
         <v>0.84</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.18</v>
+        <v>3.26</v>
       </c>
       <c r="DH4" t="n">
         <v>96.26000000000001</v>
@@ -2527,7 +2527,7 @@
         <v>5.63</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="DM4" t="n">
         <v>51.24</v>
@@ -2536,7 +2536,7 @@
         <v>0.26</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="DP4" t="n">
         <v>9.210000000000001</v>
@@ -2684,7 +2684,7 @@
         <v>0.68</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="AI5" t="n">
         <v>95.42</v>
@@ -2699,7 +2699,7 @@
         <v>4.58</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.47</v>
+        <v>0.58</v>
       </c>
       <c r="AN5" t="n">
         <v>41.58</v>
@@ -2708,7 +2708,7 @@
         <v>0.47</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.21</v>
+        <v>2.37</v>
       </c>
       <c r="AQ5" t="n">
         <v>11.26</v>
@@ -2786,10 +2786,10 @@
         <v>0.74</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.68</v>
+        <v>4.79</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.24</v>
+        <v>5.42</v>
       </c>
       <c r="BR5" t="n">
         <v>92.11</v>
@@ -2915,7 +2915,7 @@
         <v>0.68</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.24</v>
+        <v>2.37</v>
       </c>
       <c r="DH5" t="n">
         <v>94.29000000000001</v>
@@ -2930,7 +2930,7 @@
         <v>4.92</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.42</v>
+        <v>0.48</v>
       </c>
       <c r="DM5" t="n">
         <v>45.79</v>
@@ -2939,7 +2939,7 @@
         <v>0.44</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="DP5" t="n">
         <v>11.24</v>
@@ -3012,7 +3012,7 @@
         <v>108.47</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.21</v>
+        <v>-0.16</v>
       </c>
       <c r="J6" t="n">
         <v>1.05</v>
@@ -3324,7 +3324,7 @@
         <v>102.42</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.13</v>
+        <v>-0.11</v>
       </c>
       <c r="DJ6" t="n">
         <v>1.18</v>
@@ -3541,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>50.68</v>
+        <v>50.74</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>52.05</v>
+        <v>52.08</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>57.79</v>
+        <v>57.84</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>60.08</v>
+        <v>60.1</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>49.16</v>
+        <v>49.11</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>48.16</v>
+        <v>48.14</v>
       </c>
       <c r="DW10" t="n">
         <v>0.05</v>
@@ -5878,7 +5878,7 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>52.21</v>
+        <v>52.26</v>
       </c>
       <c r="Y13" t="n">
         <v>0.05</v>
@@ -5887,16 +5887,16 @@
         <v>15.53</v>
       </c>
       <c r="AA13" t="n">
-        <v>11.16</v>
+        <v>11.11</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.37</v>
+        <v>4.42</v>
       </c>
       <c r="AC13" t="n">
         <v>26.47</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AE13" t="n">
         <v>0.79</v>
@@ -5959,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>52.95</v>
+        <v>53</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -6184,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>52.58</v>
+        <v>52.63</v>
       </c>
       <c r="DW13" t="n">
         <v>0.02</v>
@@ -6193,10 +6193,10 @@
         <v>14.9</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.66</v>
+        <v>10.64</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="EA13" t="n">
         <v>25.55</v>
@@ -6230,7 +6230,7 @@
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>2.63</v>
+        <v>2.79</v>
       </c>
       <c r="H14" t="n">
         <v>96.68000000000001</v>
@@ -6245,7 +6245,7 @@
         <v>4.74</v>
       </c>
       <c r="L14" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="M14" t="n">
         <v>49.16</v>
@@ -6254,7 +6254,7 @@
         <v>0.37</v>
       </c>
       <c r="O14" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="P14" t="n">
         <v>10.68</v>
@@ -6368,10 +6368,10 @@
         <v>0.05</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.79</v>
+        <v>11.74</v>
       </c>
       <c r="BB14" t="n">
-        <v>9.210000000000001</v>
+        <v>9.16</v>
       </c>
       <c r="BC14" t="n">
         <v>2.58</v>
@@ -6413,10 +6413,10 @@
         <v>1.08</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.32</v>
+        <v>4.42</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.03</v>
+        <v>5.21</v>
       </c>
       <c r="BR14" t="n">
         <v>89.47</v>
@@ -6542,7 +6542,7 @@
         <v>0.9</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.71</v>
+        <v>2.79</v>
       </c>
       <c r="DH14" t="n">
         <v>99.52</v>
@@ -6557,7 +6557,7 @@
         <v>4.87</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="DM14" t="n">
         <v>47.92</v>
@@ -6566,7 +6566,7 @@
         <v>0.37</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DP14" t="n">
         <v>10.02</v>
@@ -6593,10 +6593,10 @@
         <v>0.05</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.08</v>
+        <v>12.06</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.789999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="DZ14" t="n">
         <v>3.29</v>
@@ -7168,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>48.74</v>
+        <v>48.68</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
@@ -7393,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.21</v>
+        <v>51.18</v>
       </c>
       <c r="DW16" t="n">
         <v>0</v>
@@ -7448,7 +7448,7 @@
         <v>-0.11</v>
       </c>
       <c r="J17" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="K17" t="n">
         <v>5.26</v>
@@ -7460,7 +7460,7 @@
         <v>43.16</v>
       </c>
       <c r="N17" t="n">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="O17" t="n">
         <v>2.58</v>
@@ -7511,7 +7511,7 @@
         <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AF17" t="n">
         <v>0.05</v>
@@ -7526,10 +7526,10 @@
         <v>93.05</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AL17" t="n">
         <v>3.47</v>
@@ -7541,7 +7541,7 @@
         <v>42.11</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="AP17" t="n">
         <v>1.37</v>
@@ -7574,7 +7574,7 @@
         <v>46.95</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="BA17" t="n">
         <v>8.109999999999999</v>
@@ -7757,10 +7757,10 @@
         <v>91.66</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="DK17" t="n">
         <v>4.36</v>
@@ -7772,7 +7772,7 @@
         <v>42.64</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="DO17" t="n">
         <v>1.98</v>
@@ -7799,7 +7799,7 @@
         <v>46.79</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="DX17" t="n">
         <v>9.68</v>
@@ -7817,7 +7817,7 @@
         <v>1.12</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="18">
@@ -7974,7 +7974,7 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>51.63</v>
+        <v>51.58</v>
       </c>
       <c r="AZ18" t="n">
         <v>0.05</v>
@@ -8199,7 +8199,7 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>51.76</v>
+        <v>51.73</v>
       </c>
       <c r="DW18" t="n">
         <v>0.02</v>
@@ -8708,10 +8708,10 @@
         <v>10.32</v>
       </c>
       <c r="AA20" t="n">
-        <v>7.84</v>
+        <v>7.89</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="AC20" t="n">
         <v>25.26</v>
@@ -9014,10 +9014,10 @@
         <v>9.369999999999999</v>
       </c>
       <c r="DY20" t="n">
-        <v>6.86</v>
+        <v>6.89</v>
       </c>
       <c r="DZ20" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="EA20" t="n">
         <v>22.84</v>
@@ -9051,7 +9051,7 @@
         <v>1.47</v>
       </c>
       <c r="G21" t="n">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="H21" t="n">
         <v>81.68000000000001</v>
@@ -9066,7 +9066,7 @@
         <v>4.53</v>
       </c>
       <c r="L21" t="n">
-        <v>0.05</v>
+        <v>0.16</v>
       </c>
       <c r="M21" t="n">
         <v>39.42</v>
@@ -9075,7 +9075,7 @@
         <v>0.32</v>
       </c>
       <c r="O21" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="P21" t="n">
         <v>11.32</v>
@@ -9102,7 +9102,7 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>48.95</v>
+        <v>48.89</v>
       </c>
       <c r="Y21" t="n">
         <v>0.05</v>
@@ -9183,7 +9183,7 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>47.79</v>
+        <v>47.84</v>
       </c>
       <c r="AZ21" t="n">
         <v>0</v>
@@ -9234,10 +9234,10 @@
         <v>1.03</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.47</v>
+        <v>4.61</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.13</v>
+        <v>5.29</v>
       </c>
       <c r="BR21" t="n">
         <v>92.11</v>
@@ -9363,7 +9363,7 @@
         <v>1.32</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="DH21" t="n">
         <v>83.97</v>
@@ -9378,7 +9378,7 @@
         <v>4.11</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DM21" t="n">
         <v>40.21</v>
@@ -9387,7 +9387,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="DP21" t="n">
         <v>11.66</v>
@@ -9408,7 +9408,7 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>48.37</v>
+        <v>48.36</v>
       </c>
       <c r="DW21" t="n">
         <v>0.02</v>

--- a/data/teams/leagues/Averages_Japan_J1_League_2025.xlsx
+++ b/data/teams/leagues/Averages_Japan_J1_League_2025.xlsx
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>55.26</v>
+        <v>55.37</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>54.15</v>
+        <v>54.21</v>
       </c>
       <c r="DW2" t="n">
         <v>0.02</v>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>44.37</v>
+        <v>44.42</v>
       </c>
       <c r="Y3" t="n">
         <v>0.05</v>
@@ -1929,19 +1929,19 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>48.58</v>
+        <v>48.53</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.11</v>
       </c>
       <c r="BA3" t="n">
-        <v>12.37</v>
+        <v>12.42</v>
       </c>
       <c r="BB3" t="n">
         <v>9.050000000000001</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.32</v>
+        <v>3.37</v>
       </c>
       <c r="BD3" t="n">
         <v>19.58</v>
@@ -2160,13 +2160,13 @@
         <v>0.08</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.92</v>
+        <v>12.94</v>
       </c>
       <c r="DY3" t="n">
         <v>8.94</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="EA3" t="n">
         <v>20.34</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>53.95</v>
+        <v>53.89</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>56.63</v>
+        <v>56.58</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.05</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>55.29</v>
+        <v>55.23</v>
       </c>
       <c r="DW4" t="n">
         <v>0.02</v>
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>42.58</v>
+        <v>42.53</v>
       </c>
       <c r="Y5" t="n">
         <v>0.05</v>
@@ -2744,16 +2744,16 @@
         <v>9.789999999999999</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.53</v>
+        <v>6.47</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="BD5" t="n">
         <v>24.68</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BF5" t="n">
         <v>1.16</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>42</v>
+        <v>41.98</v>
       </c>
       <c r="DW5" t="n">
         <v>0.02</v>
@@ -2969,16 +2969,16 @@
         <v>10.87</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.71</v>
+        <v>7.68</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="EA5" t="n">
         <v>24.95</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="EC5" t="n">
         <v>1.1</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>52.95</v>
+        <v>53</v>
       </c>
       <c r="Y6" t="n">
         <v>0.11</v>
@@ -3138,7 +3138,7 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>52.84</v>
+        <v>52.79</v>
       </c>
       <c r="AZ6" t="n">
         <v>0.05</v>
@@ -3406,7 +3406,7 @@
         <v>0.16</v>
       </c>
       <c r="F7" t="n">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="G7" t="n">
         <v>3.05</v>
@@ -3418,7 +3418,7 @@
         <v>0.11</v>
       </c>
       <c r="J7" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="K7" t="n">
         <v>5.26</v>
@@ -3460,28 +3460,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>53.42</v>
+        <v>53.47</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>12.68</v>
+        <v>12.63</v>
       </c>
       <c r="AA7" t="n">
         <v>8</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.68</v>
+        <v>4.63</v>
       </c>
       <c r="AC7" t="n">
         <v>24.79</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AF7" t="n">
         <v>0.16</v>
@@ -3541,19 +3541,19 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>50.74</v>
+        <v>50.84</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>11.32</v>
+        <v>11.37</v>
       </c>
       <c r="BB7" t="n">
         <v>7.53</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="BD7" t="n">
         <v>22.58</v>
@@ -3718,7 +3718,7 @@
         <v>0.16</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="DG7" t="n">
         <v>2.86</v>
@@ -3730,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="DK7" t="n">
         <v>5.02</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>52.08</v>
+        <v>52.15</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
@@ -3784,10 +3784,10 @@
         <v>23.68</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="8">
@@ -3809,7 +3809,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="G8" t="n">
         <v>3.26</v>
@@ -3821,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="K8" t="n">
         <v>5.89</v>
@@ -3884,7 +3884,7 @@
         <v>1.49</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF8" t="n">
         <v>0.11</v>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>57.84</v>
+        <v>57.79</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -4121,7 +4121,7 @@
         <v>0.05</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="DG8" t="n">
         <v>3</v>
@@ -4133,7 +4133,7 @@
         <v>0.02</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="DK8" t="n">
         <v>5.36</v>
@@ -4169,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>60.1</v>
+        <v>60.08</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
@@ -4190,7 +4190,7 @@
         <v>1.48</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="9">
@@ -4266,16 +4266,16 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>50.84</v>
+        <v>50.95</v>
       </c>
       <c r="Y9" t="n">
         <v>0.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.53</v>
+        <v>13.58</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.74</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="AB9" t="n">
         <v>4.79</v>
@@ -4572,16 +4572,16 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>50.82</v>
+        <v>50.87</v>
       </c>
       <c r="DW9" t="n">
         <v>0.08</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.29</v>
+        <v>13.32</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.58</v>
+        <v>8.6</v>
       </c>
       <c r="DZ9" t="n">
         <v>4.71</v>
@@ -4627,7 +4627,7 @@
         <v>-0.05</v>
       </c>
       <c r="J10" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="K10" t="n">
         <v>5.21</v>
@@ -4639,7 +4639,7 @@
         <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="O10" t="n">
         <v>2.26</v>
@@ -4669,7 +4669,7 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>49.11</v>
+        <v>49.05</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -4690,13 +4690,13 @@
         <v>1.58</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AF10" t="n">
         <v>0.05</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AH10" t="n">
         <v>2.11</v>
@@ -4708,7 +4708,7 @@
         <v>0.11</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AL10" t="n">
         <v>4.74</v>
@@ -4771,7 +4771,7 @@
         <v>1.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="BG10" t="n">
         <v>2.68</v>
@@ -4927,7 +4927,7 @@
         <v>0.02</v>
       </c>
       <c r="DF10" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="DG10" t="n">
         <v>2.5</v>
@@ -4939,7 +4939,7 @@
         <v>0.03</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="DK10" t="n">
         <v>4.98</v>
@@ -4951,7 +4951,7 @@
         <v>44.23</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="DO10" t="n">
         <v>2.42</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>48.14</v>
+        <v>48.1</v>
       </c>
       <c r="DW10" t="n">
         <v>0.05</v>
@@ -4996,7 +4996,7 @@
         <v>1.39</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="11">
@@ -5018,7 +5018,7 @@
         <v>0.16</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0.84</v>
       </c>
       <c r="G11" t="n">
         <v>2.89</v>
@@ -5030,7 +5030,7 @@
         <v>-0.05</v>
       </c>
       <c r="J11" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="K11" t="n">
         <v>4.53</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.32</v>
+        <v>12.42</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.210000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="AB11" t="n">
         <v>4.11</v>
@@ -5090,10 +5090,10 @@
         <v>23.84</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AF11" t="n">
         <v>0.05</v>
@@ -5111,7 +5111,7 @@
         <v>-0.16</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AL11" t="n">
         <v>4.37</v>
@@ -5123,7 +5123,7 @@
         <v>45.58</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="AP11" t="n">
         <v>2.05</v>
@@ -5153,7 +5153,7 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>43</v>
+        <v>42.95</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -5174,7 +5174,7 @@
         <v>1.34</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="BG11" t="n">
         <v>2.37</v>
@@ -5330,7 +5330,7 @@
         <v>0.11</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.98</v>
+        <v>0.89</v>
       </c>
       <c r="DG11" t="n">
         <v>2.58</v>
@@ -5342,7 +5342,7 @@
         <v>-0.11</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="DK11" t="n">
         <v>4.45</v>
@@ -5354,7 +5354,7 @@
         <v>47.06</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.48</v>
+        <v>0.44</v>
       </c>
       <c r="DO11" t="n">
         <v>1.84</v>
@@ -5378,16 +5378,16 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>44.66</v>
+        <v>44.64</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.1</v>
+        <v>12.16</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.210000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="DZ11" t="n">
         <v>3.89</v>
@@ -5399,7 +5399,7 @@
         <v>1.38</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="12">
@@ -5502,7 +5502,7 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="AH12" t="n">
         <v>1.58</v>
@@ -5514,7 +5514,7 @@
         <v>0.05</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AL12" t="n">
         <v>3.84</v>
@@ -5577,7 +5577,7 @@
         <v>1.19</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="BG12" t="n">
         <v>2.63</v>
@@ -5733,7 +5733,7 @@
         <v>0.02</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="DG12" t="n">
         <v>2</v>
@@ -5745,7 +5745,7 @@
         <v>-0.03</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="DK12" t="n">
         <v>4.13</v>
@@ -5802,7 +5802,7 @@
         <v>1.28</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="13">
@@ -6362,7 +6362,7 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>51.84</v>
+        <v>51.79</v>
       </c>
       <c r="AZ14" t="n">
         <v>0.05</v>
@@ -6587,7 +6587,7 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.21</v>
+        <v>51.18</v>
       </c>
       <c r="DW14" t="n">
         <v>0.05</v>
@@ -6630,7 +6630,7 @@
         <v>0.05</v>
       </c>
       <c r="F15" t="n">
-        <v>0.74</v>
+        <v>0.68</v>
       </c>
       <c r="G15" t="n">
         <v>2.21</v>
@@ -6642,7 +6642,7 @@
         <v>0.05</v>
       </c>
       <c r="J15" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="K15" t="n">
         <v>4.74</v>
@@ -6684,7 +6684,7 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>48.58</v>
+        <v>48.63</v>
       </c>
       <c r="Y15" t="n">
         <v>0.11</v>
@@ -6705,7 +6705,7 @@
         <v>1.31</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6765,7 +6765,7 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>51.26</v>
+        <v>51.21</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
@@ -6942,7 +6942,7 @@
         <v>0.02</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="DG15" t="n">
         <v>2.48</v>
@@ -6954,7 +6954,7 @@
         <v>0.05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="DK15" t="n">
         <v>4.64</v>
@@ -7011,7 +7011,7 @@
         <v>1.22</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="16">
@@ -7114,7 +7114,7 @@
         <v>0.16</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="AH16" t="n">
         <v>1.89</v>
@@ -7126,7 +7126,7 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AL16" t="n">
         <v>3.89</v>
@@ -7168,16 +7168,16 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>48.68</v>
+        <v>48.79</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.32</v>
+        <v>10.37</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.47</v>
+        <v>7.53</v>
       </c>
       <c r="BC16" t="n">
         <v>2.84</v>
@@ -7189,7 +7189,7 @@
         <v>1.04</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="BG16" t="n">
         <v>2.34</v>
@@ -7345,7 +7345,7 @@
         <v>0.14</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="DG16" t="n">
         <v>2.07</v>
@@ -7357,7 +7357,7 @@
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="DK16" t="n">
         <v>4.42</v>
@@ -7393,16 +7393,16 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.18</v>
+        <v>51.23</v>
       </c>
       <c r="DW16" t="n">
         <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.18</v>
+        <v>12.21</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.34</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DZ16" t="n">
         <v>3.84</v>
@@ -7414,7 +7414,7 @@
         <v>1.31</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="17">
@@ -7920,7 +7920,7 @@
         <v>0.11</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="AH18" t="n">
         <v>2.74</v>
@@ -7944,7 +7944,7 @@
         <v>40.32</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="AP18" t="n">
         <v>1.79</v>
@@ -8151,7 +8151,7 @@
         <v>0.14</v>
       </c>
       <c r="DF18" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="DG18" t="n">
         <v>2.61</v>
@@ -8175,7 +8175,7 @@
         <v>42.24</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="DO18" t="n">
         <v>2.1</v>
@@ -8762,7 +8762,7 @@
         <v>11.37</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.42</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="AT20" t="n">
         <v>1.32</v>
@@ -8780,7 +8780,7 @@
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>39.05</v>
+        <v>39</v>
       </c>
       <c r="AZ20" t="n">
         <v>0.05</v>
@@ -8993,7 +8993,7 @@
         <v>11.06</v>
       </c>
       <c r="DR20" t="n">
-        <v>8.130000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
@@ -9005,7 +9005,7 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>40.9</v>
+        <v>40.87</v>
       </c>
       <c r="DW20" t="n">
         <v>0.08</v>
@@ -9183,7 +9183,7 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>47.84</v>
+        <v>47.79</v>
       </c>
       <c r="AZ21" t="n">
         <v>0</v>
@@ -9408,7 +9408,7 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>48.36</v>
+        <v>48.34</v>
       </c>
       <c r="DW21" t="n">
         <v>0.02</v>

--- a/data/teams/leagues/Averages_Japan_J1_League_2025.xlsx
+++ b/data/teams/leagues/Averages_Japan_J1_League_2025.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -706,667 +694,667 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>total_games</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>home_games</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>away_games</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>home_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>home_avg_2h_cards</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>home_avg_2h_corners</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>home_avg_attacks</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>home_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>home_avg_cards_num</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>home_avg_corners</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>home_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>home_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>home_avg_fh_cards</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>home_avg_fh_corners</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>home_avg_fouls</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>home_avg_freekicks</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>home_avg_goalkicks</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>home_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>home_avg_goals_scored</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>home_avg_penalties_won</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>home_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>home_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>home_avg_possession</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>home_avg_red_cards</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>home_avg_shots</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>home_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>home_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>home_avg_throwins</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>home_avg_xg</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>home_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>away_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>away_avg_2h_cards</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>away_avg_2h_corners</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>away_avg_attacks</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>away_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>away_avg_cards_num</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>away_avg_corners</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>away_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>away_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>away_avg_fh_cards</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>away_avg_fh_corners</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>away_avg_fouls</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>away_avg_freekicks</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>away_avg_goalkicks</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>away_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>away_avg_goals_scored</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>away_avg_penalties_won</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>away_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>away_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>away_avg_possession</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>away_avg_red_cards</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>away_avg_shots</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>away_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>away_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>away_avg_throwins</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>away_avg_xg</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>away_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>totalGoalCount</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>totalCornerCount</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>overallGoalCount</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ht_goals_team_a</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>ht_goals_team_b</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>goals_2hg_team_a</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>goals_2hg_team_b</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>GoalCount_2hg</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>HTGoalCount</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>corner_fh_count</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>corner_2h_count</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>over05</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>over15</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>over25</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>over35</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>over45</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>over55</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>btts</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>avg_odds_ft_1</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_1_odd</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>avg_odds_ft_x</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_x_odd</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>avg_odds_ft_2</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_2_odd</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over05</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over15</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under05</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under15</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>avg_odds_btts_no</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>avg_odds_btts_yes</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_85</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_95</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_85</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_95</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over15</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over25</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over35</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over05_odd</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over15_odd</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under05_odd</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under15_odd</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_no_odd</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_yes_odd</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_85_odd</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_95_odd</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_85_odd</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_95_odd</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over15_odd</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over25_odd</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over35_odd</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>total_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>total_avg_2h_cards</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>total_avg_2h_corners</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>total_avg_attacks</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>total_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>total_avg_cards_num</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>total_avg_corners</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>total_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>total_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>total_avg_fh_cards</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>total_avg_fh_corners</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>total_avg_fouls</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>total_avg_freekicks</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>total_avg_goalkicks</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>total_avg_penalties_won</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>total_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>total_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>total_avg_possession</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>total_avg_red_cards</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>total_avg_shots</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>total_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>total_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>total_avg_throwins</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>total_avg_xg</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>total_avg_yellow_cards</t>
         </is>
